--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,242 +1029,242 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>21.24</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>20.46</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2230.740606936416</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>498.6</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>637.64</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>350.72</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>2233.575976845152</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>718.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>644.72</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>12.9286283891547</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>17.20463480240016</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-19.53786595693201</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>4.46</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>283.07</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
           <t>21.9</t>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,72 +1324,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,47 +1440,47 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1490,27 +1490,27 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-66.53</t>
+          <t>-66.69</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2233.575976845152</t>
+          <t>2230.740606936416</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>718.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>529.4</t>
+          <t>619.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>630.6</t>
+          <t>644.72</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>14.83051744603433</t>
+          <t>21.15202049006009</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>19.72</v>
+        <v>55.92</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,37 +1608,37 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>12.9286283891547</t>
+          <t>24.76679104477612</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>17.20463480240016</t>
+          <t>-40.08623103197267</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-19.53786595693201</t>
+          <t>-21.81323434808007</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>960</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,72 +1871,72 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>64.95</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-66.28</t>
+          <t>-66.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2233.575976845152</t>
+          <t>2230.740606936416</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>706.8</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>568.7</t>
+          <t>529.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>632.6</t>
+          <t>630.6</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>13.94142981484174</t>
+          <t>14.83051744603433</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>46.27</v>
+        <v>19.72</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,37 +2039,37 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>12.9286283891547</t>
+          <t>24.76679104477612</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>17.20463480240016</t>
+          <t>-40.08623103197267</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-19.53786595693201</t>
+          <t>-21.81323434808007</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>960</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>58.87</t>
+          <t>24.28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.95</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-66.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2233.575976845152</t>
+          <t>2230.740606936416</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>897.6</t>
+          <t>706.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>568.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>643.38</t>
+          <t>632.6</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>138</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>8.064144510457766</t>
+          <t>13.94142981484174</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>105.57</v>
+        <v>46.27</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2470,32 +2470,32 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>12.9286283891547</t>
+          <t>24.76679104477612</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>17.20463480240016</t>
+          <t>-40.08623103197267</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-19.53786595693201</t>
+          <t>-21.81323434808007</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>960</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,22 +2550,22 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>58.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,67 +2733,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2233.575976845152</t>
+          <t>2230.740606936416</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1281.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>897.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>485.5</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>627.28</t>
+          <t>643.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>332</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-9.664682822420978</t>
+          <t>8.064144510457766</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>94.28</v>
+        <v>105.57</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,37 +2901,37 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>12.9286283891547</t>
+          <t>24.76679104477612</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>17.20463480240016</t>
+          <t>-40.08623103197267</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-19.53786595693201</t>
+          <t>-21.81323434808007</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>960</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,59 +3184,59 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-69.18</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2233.575976845152</t>
+          <t>2230.740606936416</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>1281.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>519.6</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>368.3</t>
+          <t>485.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>605.38</t>
+          <t>627.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>287</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-28.56287576940888</t>
+          <t>-9.664682822420978</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>37.38</v>
+        <v>94.28</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,37 +3332,37 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>12.9286283891547</t>
+          <t>24.76679104477612</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>17.20463480240016</t>
+          <t>-40.08623103197267</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-19.53786595693201</t>
+          <t>-21.81323434808007</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>960</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,74 +3479,74 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>41.08</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-1.41</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>35.89</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>19.95</t>
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,33 +3574,33 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,59 +3615,59 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.89</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-69.47</t>
+          <t>-69.18</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2233.575976845152</t>
+          <t>2230.740606936416</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>879.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>470.6</t>
+          <t>519.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>346.3</t>
+          <t>368.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>610.86</t>
+          <t>605.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>151</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-40.55185680677671</t>
+          <t>-28.56287576940888</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>52.26</v>
+        <v>37.38</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,37 +3763,37 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>12.9286283891547</t>
+          <t>24.76679104477612</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>17.20463480240016</t>
+          <t>-40.08623103197267</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-19.53786595693201</t>
+          <t>-21.81323434808007</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>960</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,27 +3920,27 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>62.92</t>
+          <t>35.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4046,255 +4046,255 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>20.96</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-69.47</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>2230.740606936416</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>879.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>470.6</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>346.3</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>610.86</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-40.55185680677671</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>15.78</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>350.72</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-4.49</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-69.53</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>2233.575976845152</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>1025.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>430.6</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>264.3</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>593.48</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-57.42629635787348</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>12.9286283891547</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>17.20463480240016</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-19.53786595693201</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>4.46</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>283.07</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,52 +4477,52 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-69.18</t>
+          <t>-69.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2233.575976845152</t>
+          <t>2230.740606936416</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>1025.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>232.4</t>
+          <t>430.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>169.7</t>
+          <t>264.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>574.68</t>
+          <t>593.48</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>166</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-70.99858252086703</t>
+          <t>-57.42629635787348</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-49.09</v>
+        <v>17.22</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>14.44</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>12.9286283891547</t>
+          <t>24.76679104477612</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>17.20463480240016</t>
+          <t>-40.08623103197267</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-19.53786595693201</t>
+          <t>-21.81323434808007</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>960</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,69 +4772,69 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.23</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,33 +4867,33 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,127 +4903,127 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.62</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-9.62</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-69.18</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>2230.740606936416</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>309.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>232.4</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>169.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>574.68</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-70.99858252086703</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-49.09</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-15.44</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-68.44</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>2233.575976845152</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>198.0</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>198.8</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>571.72</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-74.98224146047521</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-65.34999999999999</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
       <c r="BF11" t="inlineStr">
         <is>
           <t>2025/09/11</t>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>14.44</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>12.9286283891547</t>
+          <t>24.76679104477612</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>17.20463480240016</t>
+          <t>-40.08623103197267</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-19.53786595693201</t>
+          <t>-21.81323434808007</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>960</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>65.96</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.45</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-23.04</t>
+          <t>-15.44</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-67.22</t>
+          <t>-68.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2233.575976845152</t>
+          <t>2230.740606936416</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>226.5</t>
+          <t>198.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>572.76</t>
+          <t>571.72</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-76.73370217279458</t>
+          <t>-74.98224146047521</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-54.64</v>
+        <v>-65.34999999999999</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>12.9286283891547</t>
+          <t>24.76679104477612</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>17.20463480240016</t>
+          <t>-40.08623103197267</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-19.53786595693201</t>
+          <t>-21.81323434808007</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>283.07</t>
+          <t>350.72</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>960</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,22 +5567,22 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>文化創意業右上上櫃</t>
+          <t>文化創意業平上櫃</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,74 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-67.00</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2230.740606936416</t>
+          <t>2227.709956709957</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>498.6</t>
+          <t>329.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>613.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>637.64</t>
+          <t>638.44</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>-284</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>20.468960648762</t>
+          <t>14.51967735451805</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>16.71</v>
+        <v>-18.2</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1460,242 +1460,242 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>21.24</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>20.46</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>2227.709956709957</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>498.6</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>637.64</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>4.48</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>347.38</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>2230.740606936416</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>718.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>644.72</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>4.55</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>350.72</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
           <t>21.9</t>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,87 +1740,87 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>47.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>-2.1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,42 +1876,42 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1921,27 +1921,27 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-66.53</t>
+          <t>-66.69</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2230.740606936416</t>
+          <t>2227.709956709957</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>718.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>529.4</t>
+          <t>619.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>630.6</t>
+          <t>644.72</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>14.83051744603433</t>
+          <t>21.15202049006009</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>19.72</v>
+        <v>55.92</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,67 +2307,67 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>64.95</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-66.28</t>
+          <t>-66.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2230.740606936416</t>
+          <t>2227.709956709957</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>706.8</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>568.7</t>
+          <t>529.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>632.6</t>
+          <t>630.6</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>13.94142981484174</t>
+          <t>14.83051744603433</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>46.27</v>
+        <v>19.72</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.87</t>
+          <t>24.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.95</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-66.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2230.740606936416</t>
+          <t>2227.709956709957</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>897.6</t>
+          <t>706.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>568.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>643.38</t>
+          <t>632.6</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>138</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>8.064144510457766</t>
+          <t>13.94142981484174</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>105.57</v>
+        <v>46.27</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>58.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,62 +3169,62 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2230.740606936416</t>
+          <t>2227.709956709957</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1281.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>897.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>485.5</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>627.28</t>
+          <t>643.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>332</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-9.664682822420978</t>
+          <t>8.064144510457766</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>94.28</v>
+        <v>105.57</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,59 +3615,59 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-69.18</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2230.740606936416</t>
+          <t>2227.709956709957</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>1281.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>519.6</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>368.3</t>
+          <t>485.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>605.38</t>
+          <t>627.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>287</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-28.56287576940888</t>
+          <t>-9.664682822420978</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>37.38</v>
+        <v>94.28</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,74 +3910,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.17</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>41.08</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>35.89</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>19.95</t>
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,22 +4005,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4046,59 +4046,59 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.89</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-69.47</t>
+          <t>-69.18</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2230.740606936416</t>
+          <t>2227.709956709957</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>879.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>470.6</t>
+          <t>519.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>346.3</t>
+          <t>368.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>610.86</t>
+          <t>605.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>151</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-40.55185680677671</t>
+          <t>-28.56287576940888</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>52.26</v>
+        <v>37.38</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,22 +4351,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>62.92</t>
+          <t>35.89</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,255 +4477,255 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>20.96</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-69.47</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>2227.709956709957</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>879.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>470.6</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>346.3</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>610.86</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-40.55185680677671</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>15.78</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>4.48</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>347.38</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-4.49</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-69.53</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>2230.740606936416</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>1025.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>430.6</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>264.3</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>593.48</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-57.42629635787348</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>4.55</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>350.72</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,52 +4908,52 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-69.18</t>
+          <t>-69.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2230.740606936416</t>
+          <t>2227.709956709957</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>1025.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>232.4</t>
+          <t>430.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>169.7</t>
+          <t>264.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>574.68</t>
+          <t>593.48</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>166</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-70.99858252086703</t>
+          <t>-57.42629635787348</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-49.09</v>
+        <v>17.22</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>14.44</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,69 +5203,69 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>21.4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.48</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.23</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-0.40</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,22 +5298,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,127 +5334,127 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>21.16</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.62</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-9.62</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-69.18</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>2227.709956709957</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>309.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>232.4</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>169.7</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>574.68</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-70.99858252086703</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>-49.09</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-15.44</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-68.44</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>2230.740606936416</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>198.0</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>198.8</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>571.72</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-74.98224146047521</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-65.34999999999999</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
       <c r="BF12" t="inlineStr">
         <is>
           <t>2025/09/11</t>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>14.44</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>350.72</t>
+          <t>347.38</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>945</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-69.81</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2227.709956709957</t>
+          <t>2224.742074927954</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>329.6</t>
+          <t>337.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>613.6</t>
+          <t>522.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>638.44</t>
+          <t>629.48</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-284</t>
+          <t>-184</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>14.51967735451805</t>
+          <t>6.084218554662919</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-18.2</v>
+        <v>-40.31</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,74 +1445,74 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-67.00</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2227.709956709957</t>
+          <t>2224.742074927954</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>498.6</t>
+          <t>329.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>613.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>637.64</t>
+          <t>638.44</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>-284</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>20.468960648762</t>
+          <t>14.51967735451805</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>16.71</v>
+        <v>-18.2</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,242 +1891,242 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>21.24</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>20.46</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>2224.742074927954</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>498.6</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>637.64</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>341.19</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>2227.709956709957</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>718.6</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>644.72</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>4.48</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>347.38</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
           <t>21.9</t>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,72 +2186,72 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-4.29</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,42 +2307,42 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2352,27 +2352,27 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-66.53</t>
+          <t>-66.69</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2227.709956709957</t>
+          <t>2224.742074927954</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>718.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>529.4</t>
+          <t>619.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>630.6</t>
+          <t>644.72</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>14.83051744603433</t>
+          <t>21.15202049006009</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>19.72</v>
+        <v>55.92</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,67 +2738,67 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>64.95</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-66.28</t>
+          <t>-66.53</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2227.709956709957</t>
+          <t>2224.742074927954</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>706.8</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>568.7</t>
+          <t>529.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>632.6</t>
+          <t>630.6</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>13.94142981484174</t>
+          <t>14.83051744603433</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>46.27</v>
+        <v>19.72</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>58.87</t>
+          <t>24.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.95</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-66.28</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2227.709956709957</t>
+          <t>2224.742074927954</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>897.6</t>
+          <t>706.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>568.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>643.38</t>
+          <t>632.6</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>138</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>8.064144510457766</t>
+          <t>13.94142981484174</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>105.57</v>
+        <v>46.27</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>58.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,62 +3600,62 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2227.709956709957</t>
+          <t>2224.742074927954</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1281.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>897.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>485.5</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>627.28</t>
+          <t>643.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>332</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-9.664682822420978</t>
+          <t>8.064144510457766</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>94.28</v>
+        <v>105.57</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4046,59 +4046,59 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-69.18</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2227.709956709957</t>
+          <t>2224.742074927954</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>1281.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>519.6</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>368.3</t>
+          <t>485.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>605.38</t>
+          <t>627.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>287</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-28.56287576940888</t>
+          <t>-9.664682822420978</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>37.38</v>
+        <v>94.28</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,74 +4341,74 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-3.33</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>41.08</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.48</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>35.89</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>19.95</t>
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,22 +4436,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,59 +4477,59 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.89</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-69.47</t>
+          <t>-69.18</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2227.709956709957</t>
+          <t>2224.742074927954</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>879.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>470.6</t>
+          <t>519.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>346.3</t>
+          <t>368.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>610.86</t>
+          <t>605.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>151</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-40.55185680677671</t>
+          <t>-28.56287576940888</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>52.26</v>
+        <v>37.38</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,22 +4782,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>62.92</t>
+          <t>35.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,255 +4908,255 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>20.96</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-69.47</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>2224.742074927954</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>879.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>470.6</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>346.3</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>610.86</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-40.55185680677671</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>15.78</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>341.19</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-4.49</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-69.53</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>2227.709956709957</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>1025.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>430.6</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>264.3</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>593.48</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-57.42629635787348</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>4.48</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>347.38</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,52 +5339,52 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>20.95</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-69.18</t>
+          <t>-69.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2227.709956709957</t>
+          <t>2224.742074927954</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>309.0</t>
+          <t>1025.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>232.4</t>
+          <t>430.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>169.7</t>
+          <t>264.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>574.68</t>
+          <t>593.48</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>166</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-70.99858252086703</t>
+          <t>-57.42629635787348</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-49.09</v>
+        <v>17.22</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>14.44</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>347.38</t>
+          <t>341.19</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>925</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-35.32</t>
+          <t>-33.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.34</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-69.81</t>
+          <t>-72.31</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2224.742074927954</t>
+          <t>2221.700719424461</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>337.8</t>
+          <t>295.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>522.3</t>
+          <t>441.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>629.48</t>
+          <t>627.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-184</t>
+          <t>-146</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>6.084218554662919</t>
+          <t>-3.717912235274216</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-40.31</v>
+        <v>-57.63</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-69.81</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2224.742074927954</t>
+          <t>2221.700719424461</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>329.6</t>
+          <t>337.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>613.6</t>
+          <t>522.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>638.44</t>
+          <t>629.48</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-284</t>
+          <t>-184</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>14.51967735451805</t>
+          <t>6.084218554662919</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-18.2</v>
+        <v>-40.31</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,79 +1871,79 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-67.00</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2224.742074927954</t>
+          <t>2221.700719424461</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>498.6</t>
+          <t>329.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>613.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>637.64</t>
+          <t>638.44</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>-284</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>20.468960648762</t>
+          <t>14.51967735451805</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>16.71</v>
+        <v>-18.2</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,17 +2302,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,242 +2322,242 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>21.24</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>20.46</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>2221.700719424461</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>498.6</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>637.64</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>342.2</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>2224.742074927954</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>718.6</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>644.72</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>341.19</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
           <t>21.9</t>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,72 +2617,72 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-4.29</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,47 +2733,47 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-66.53</t>
+          <t>-66.69</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2224.742074927954</t>
+          <t>2221.700719424461</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>718.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>529.4</t>
+          <t>619.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>630.6</t>
+          <t>644.72</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>14.83051744603433</t>
+          <t>21.15202049006009</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>19.72</v>
+        <v>55.92</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,72 +3164,72 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>64.95</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-66.28</t>
+          <t>-66.53</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2224.742074927954</t>
+          <t>2221.700719424461</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>706.8</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>568.7</t>
+          <t>529.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>632.6</t>
+          <t>630.6</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>13.94142981484174</t>
+          <t>14.83051744603433</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>46.27</v>
+        <v>19.72</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>58.87</t>
+          <t>24.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.95</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-66.28</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2224.742074927954</t>
+          <t>2221.700719424461</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>897.6</t>
+          <t>706.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>568.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>643.38</t>
+          <t>632.6</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>138</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>8.064144510457766</t>
+          <t>13.94142981484174</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>105.57</v>
+        <v>46.27</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3783,12 +3783,12 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>58.87</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,67 +4026,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2224.742074927954</t>
+          <t>2221.700719424461</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1281.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>897.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>485.5</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>627.28</t>
+          <t>643.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>332</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-9.664682822420978</t>
+          <t>8.064144510457766</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>94.28</v>
+        <v>105.57</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,59 +4477,59 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-69.18</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2224.742074927954</t>
+          <t>2221.700719424461</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>1281.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>519.6</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>368.3</t>
+          <t>485.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>605.38</t>
+          <t>627.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>287</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-28.56287576940888</t>
+          <t>-9.664682822420978</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>37.38</v>
+        <v>94.28</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,74 +4772,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-3.33</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>41.08</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-3.1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>35.89</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>19.95</t>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,33 +4867,33 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,59 +4908,59 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.89</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-69.47</t>
+          <t>-69.18</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2224.742074927954</t>
+          <t>2221.700719424461</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>879.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>470.6</t>
+          <t>519.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>346.3</t>
+          <t>368.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>610.86</t>
+          <t>605.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>151</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-40.55185680677671</t>
+          <t>-28.56287576940888</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>52.26</v>
+        <v>37.38</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>15.78</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>341.19</t>
+          <t>342.2</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,22 +5213,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>62.92</t>
+          <t>35.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,255 +5339,255 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>20.96</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-69.47</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>2221.700719424461</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>879.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>470.6</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>346.3</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>610.86</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-40.55185680677671</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>15.78</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>342.2</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>20.95</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.71</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>18.8</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-4.49</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-69.53</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>2224.742074927954</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>1025.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>430.6</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>264.3</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>593.48</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-57.42629635787348</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>14.97</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>341.19</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>21.9</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,34 +883,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>-1.4</t>
@@ -913,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-33.14</t>
+          <t>-72.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-47.47</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-72.31</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2221.700719424461</t>
+          <t>2218.771551724138</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>295.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>441.8</t>
+          <t>416.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>627.74</t>
+          <t>628.1</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>-301</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3.717912235274216</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-57.63</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-13.10162873834002</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-64.71206950520195</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>122</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>12.30</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>11.76</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>20.4</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-35.32</t>
+          <t>-33.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1455,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.34</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-69.81</t>
+          <t>-72.31</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,198 +1540,203 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2221.700719424461</t>
+          <t>2218.771551724138</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>337.8</t>
+          <t>295.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>522.3</t>
+          <t>441.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>629.48</t>
+          <t>627.74</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-184</t>
+          <t>-146</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>6.084218554662919</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-40.31</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3.717912235274216</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-57.62963157992846</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>74</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>12.30</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價跌量-</t>
-        </is>
-      </c>
       <c r="BR3" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>21.0</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>21.0</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-69.81</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2221.700719424461</t>
+          <t>2218.771551724138</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>329.6</t>
+          <t>337.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>613.6</t>
+          <t>522.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>638.44</t>
+          <t>629.48</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-284</t>
+          <t>-184</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>14.51967735451805</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>6.084218554662919</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-40.31080484454031</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>112</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>12.30</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,283 +2327,288 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>6.49</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>21.66</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>21.26</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>20.55</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-11.33</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-67.90</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>2218.771551724138</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>329.6</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>613.6</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>638.44</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-284</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>14.51967735451805</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-18.20138076382364</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>87</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>14.71</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
           <t>0.32</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>6.33</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>21.73</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>21.24</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>20.46</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>19.24</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-3.66</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-67.00</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>2221.700719424461</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>181.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>498.6</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>635.8</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>637.64</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-137</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>20.468960648762</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>16.58</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>21.85</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,12 +2763,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2753,268 +2778,273 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>21.24</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>20.46</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>2218.771551724138</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>498.6</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>637.64</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>16.7121315216225</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>181</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>338.68</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>文化創意業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>2221.700719424461</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>718.6</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>644.72</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>21.9</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,72 +3078,72 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-4.78</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-1.67</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,42 +3199,42 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3214,27 +3244,27 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-66.53</t>
+          <t>-66.69</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2221.700719424461</t>
+          <t>2218.771551724138</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>718.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>529.4</t>
+          <t>619.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>630.6</t>
+          <t>644.72</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>14.83051744603433</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
+          <t>21.15202049006009</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>55.92028723220176</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>1023</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>17.11</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
         <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3559,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,67 +3635,67 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>64.95</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-66.28</t>
+          <t>-66.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2221.700719424461</t>
+          <t>2218.771551724138</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>706.8</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>568.7</t>
+          <t>529.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>632.6</t>
+          <t>630.6</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>13.94142981484174</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>46.27</v>
-      </c>
-      <c r="BD8" t="inlineStr">
+          <t>14.83051744603433</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>19.7204994175936</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>286</v>
+      </c>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>16.58</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>14.17</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>21.8</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3920,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>58.87</t>
+          <t>24.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4005,12 +4045,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4031,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.95</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-66.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,180 +4156,180 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2221.700719424461</t>
+          <t>2218.771551724138</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>897.6</t>
+          <t>706.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>568.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>643.38</t>
+          <t>632.6</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>138</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>8.064144510457766</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>105.57</v>
-      </c>
-      <c r="BD9" t="inlineStr">
+          <t>13.94142981484174</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>46.26649898895357</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>71</v>
+      </c>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>16.58</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>1.66</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>21.7</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4299,15 +4339,20 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>58.87</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,62 +4507,62 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4527,7 +4572,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2221.700719424461</t>
+          <t>2218.771551724138</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1281.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>897.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>485.5</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>627.28</t>
+          <t>643.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>332</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-9.664682822420978</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>94.28</v>
-      </c>
-      <c r="BD10" t="inlineStr">
+          <t>8.064144510457766</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>105.5726948412909</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>932</v>
+      </c>
+      <c r="BE10" t="inlineStr">
         <is>
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>19.79</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>21.95</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,7 +4943,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,59 +4958,59 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-69.18</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2221.700719424461</t>
+          <t>2218.771551724138</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>1281.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>519.6</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>368.3</t>
+          <t>485.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>605.38</t>
+          <t>627.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>287</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-28.56287576940888</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>37.38</v>
-      </c>
-      <c r="BD11" t="inlineStr">
+          <t>-9.664682822420978</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>94.27537838601245</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>1281</v>
+      </c>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>16.04</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>19.79</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,74 +5258,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-3.83</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>41.08</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-3.1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>35.89</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>19.95</t>
@@ -5283,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,22 +5353,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -5324,7 +5379,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,59 +5394,59 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.52</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.96</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.89</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-69.47</t>
+          <t>-69.18</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,172 +5464,172 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2221.700719424461</t>
+          <t>2218.771551724138</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>879.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>470.6</t>
+          <t>519.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>346.3</t>
+          <t>368.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>610.86</t>
+          <t>605.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>151</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-40.55185680677671</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>52.26</v>
-      </c>
-      <c r="BD12" t="inlineStr">
+          <t>-28.56287576940888</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>37.37651993611422</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>371</v>
+      </c>
+      <c r="BE12" t="inlineStr">
         <is>
           <t>2025-11-13</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>15.78</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>16.04</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>4.38</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>342.2</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>338.68</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>文化創意業平上櫃</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
           <t>21.65</t>
@@ -5582,25 +5637,30 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-72.37</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>25.79</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.87</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-47.47</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2218.771551724138</t>
+          <t>2223.565997130559</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>820.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>416.9</t>
+          <t>659.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>628.1</t>
+          <t>579.76</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-301</t>
+          <t>160</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-13.10162873834002</t>
+          <t>19.80985655751795</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-64.71206950520195</t>
+          <t>200.8230256847368</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>122</v>
+        <v>3707</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1267,27 +1267,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-33.14</t>
+          <t>-72.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-47.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-72.31</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2218.771551724138</t>
+          <t>2223.565997130559</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>295.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>441.8</t>
+          <t>416.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>627.74</t>
+          <t>628.1</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>-301</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3.717912235274216</t>
+          <t>-13.10162873834002</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-57.62963157992846</t>
+          <t>-64.71206950520195</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1703,27 +1703,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-35.32</t>
+          <t>-33.14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.34</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-69.81</t>
+          <t>-72.31</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2218.771551724138</t>
+          <t>2223.565997130559</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>337.8</t>
+          <t>295.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>522.3</t>
+          <t>441.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>629.48</t>
+          <t>627.74</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-184</t>
+          <t>-146</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>6.084218554662919</t>
+          <t>-3.717912235274216</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-40.31080484454031</t>
+          <t>-57.62963157992846</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,182 +2322,182 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-69.81</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>2223.565997130559</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>337.8</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>522.3</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>629.48</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-184</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>6.084218554662919</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-40.31080484454031</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>112</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>12.30</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-67.90</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>2218.771551724138</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>329.6</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>613.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>638.44</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-284</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>14.51967735451805</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-18.20138076382364</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>87</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
       <c r="BN5" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2575,27 +2575,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,79 +2758,79 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-67.00</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2218.771551724138</t>
+          <t>2223.565997130559</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>498.6</t>
+          <t>329.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>613.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>637.64</t>
+          <t>638.44</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>-284</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>20.468960648762</t>
+          <t>14.51967735451805</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>16.7121315216225</t>
+          <t>-18.20138076382364</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3011,27 +3011,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,17 +3194,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3214,247 +3214,247 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>21.24</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>20.46</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>2223.565997130559</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>498.6</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>637.64</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>16.7121315216225</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>181</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>4.79</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>342.05</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>2218.771551724138</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>718.6</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>644.72</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>55.92028723220176</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>1023</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>4.36</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>338.68</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>文化創意業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
           <t>21.9</t>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,72 +3514,72 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4.58</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.15</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,47 +3630,47 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3680,27 +3680,27 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-66.53</t>
+          <t>-66.69</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,50 +3720,50 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2218.771551724138</t>
+          <t>2223.565997130559</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>718.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>529.4</t>
+          <t>619.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>630.6</t>
+          <t>644.72</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>14.83051744603433</t>
+          <t>21.15202049006009</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>19.7204994175936</t>
+          <t>55.92028723220176</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>286</v>
+        <v>1023</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3883,27 +3883,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,72 +4066,72 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>64.95</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-66.28</t>
+          <t>-66.53</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2218.771551724138</t>
+          <t>2223.565997130559</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>706.8</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>568.7</t>
+          <t>529.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>632.6</t>
+          <t>630.6</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>13.94142981484174</t>
+          <t>14.83051744603433</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>46.26649898895357</t>
+          <t>19.7204994175936</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>71</v>
+        <v>286</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4319,27 +4319,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>58.87</t>
+          <t>24.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.95</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-66.28</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2218.771551724138</t>
+          <t>2223.565997130559</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>897.6</t>
+          <t>706.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>568.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>643.38</t>
+          <t>632.6</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>138</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>8.064144510457766</t>
+          <t>13.94142981484174</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>105.5726948412909</t>
+          <t>46.26649898895357</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>932</v>
+        <v>71</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4755,22 +4755,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>58.87</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,67 +4938,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2218.771551724138</t>
+          <t>2223.565997130559</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1281.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>897.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>485.5</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>627.28</t>
+          <t>643.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>332</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-9.664682822420978</t>
+          <t>8.064144510457766</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>94.27537838601245</t>
+          <t>105.5726948412909</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1281</v>
+        <v>932</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5191,27 +5191,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5394,59 +5394,59 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.52</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>15.96</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-69.18</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2218.771551724138</t>
+          <t>2223.565997130559</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>1281.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>519.6</t>
+          <t>773.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>368.3</t>
+          <t>485.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>605.38</t>
+          <t>627.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>287</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-28.56287576940888</t>
+          <t>-9.664682822420978</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>37.37651993611422</t>
+          <t>94.27537838601245</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>371</v>
+        <v>1281</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>19.79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>338.68</t>
+          <t>342.05</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5627,27 +5627,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>文化創意業平上櫃</t>
+          <t>文化創意業右上上櫃</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.65</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.75</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,113 +913,113 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.40</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,60 +1094,60 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-73.03</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2223.565997130559</t>
+          <t>2237.112464183381</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>820.4</t>
+          <t>2360.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>1344.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>579.76</t>
+          <t>694.98</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>19.80985655751795</t>
+          <t>122.5471119602961</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>200.8230256847368</t>
+          <t>687.6020166755757</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>3707</v>
+        <v>7786</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-72.37</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,54 +1364,54 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1419,27 +1419,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>25.79</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,72 +1450,72 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.87</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-47.47</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2223.565997130559</t>
+          <t>2237.112464183381</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>820.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>416.9</t>
+          <t>659.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>628.1</t>
+          <t>579.76</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-301</t>
+          <t>160</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-13.10162873834002</t>
+          <t>19.80985655751795</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-64.71206950520195</t>
+          <t>200.8230256847368</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>122</v>
+        <v>3707</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.14</t>
+          <t>-72.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,54 +1800,54 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1855,27 +1855,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-47.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-72.31</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2223.565997130559</t>
+          <t>2237.112464183381</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>295.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>441.8</t>
+          <t>416.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>627.74</t>
+          <t>628.1</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>-301</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3.717912235274216</t>
+          <t>-13.10162873834002</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-57.62963157992846</t>
+          <t>-64.71206950520195</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>12.86</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-35.32</t>
+          <t>-33.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,54 +2236,54 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2291,27 +2291,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.34</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-69.81</t>
+          <t>-72.31</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2223.565997130559</t>
+          <t>2237.112464183381</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>337.8</t>
+          <t>295.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>522.3</t>
+          <t>441.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>629.48</t>
+          <t>627.74</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-184</t>
+          <t>-146</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>6.084218554662919</t>
+          <t>-3.717912235274216</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-40.31080484454031</t>
+          <t>-57.62963157992846</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>12.86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,54 +2672,54 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2727,27 +2727,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,182 +2758,182 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-69.81</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>2237.112464183381</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>337.8</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>522.3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>629.48</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-184</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>6.084218554662919</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-40.31080484454031</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>112</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>12.30</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-67.90</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>2223.565997130559</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>329.6</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>613.6</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>638.44</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-284</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>14.51967735451805</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-18.20138076382364</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>87</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>14.71</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,54 +3108,54 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3163,27 +3163,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,79 +3194,79 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-67.00</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2223.565997130559</t>
+          <t>2237.112464183381</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>498.6</t>
+          <t>329.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>613.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>637.64</t>
+          <t>638.44</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>-284</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>20.468960648762</t>
+          <t>14.51967735451805</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>16.7121315216225</t>
+          <t>-18.20138076382364</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,54 +3544,54 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3599,27 +3599,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3650,247 +3650,247 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>21.24</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>20.46</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>2237.112464183381</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>498.6</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>637.64</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>16.7121315216225</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>181</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>5.03</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>346.59</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>2223.565997130559</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>718.6</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>644.72</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>55.92028723220176</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>1023</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>4.79</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>342.05</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
           <t>21.9</t>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,112 +3950,112 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>9.13</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.39</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>6.97</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,47 +4066,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4116,27 +4116,27 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,60 +4146,60 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-66.53</t>
+          <t>-66.69</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2223.565997130559</t>
+          <t>2237.112464183381</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>718.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>529.4</t>
+          <t>619.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>630.6</t>
+          <t>644.72</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>14.83051744603433</t>
+          <t>21.15202049006009</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>19.7204994175936</t>
+          <t>55.92028723220176</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>286</v>
+        <v>1023</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,82 +4416,82 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,72 +4502,72 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>64.95</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-66.28</t>
+          <t>-66.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2223.565997130559</t>
+          <t>2237.112464183381</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>706.8</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>568.7</t>
+          <t>529.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>632.6</t>
+          <t>630.6</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>13.94142981484174</t>
+          <t>14.83051744603433</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>46.26649898895357</t>
+          <t>19.7204994175936</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>71</v>
+        <v>286</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>58.87</t>
+          <t>24.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,54 +4852,54 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0.69</t>
@@ -4907,22 +4907,22 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.95</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-66.28</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2223.565997130559</t>
+          <t>2237.112464183381</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>897.6</t>
+          <t>706.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>568.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>643.38</t>
+          <t>632.6</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>138</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>8.064144510457766</t>
+          <t>13.94142981484174</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>105.5726948412909</t>
+          <t>46.26649898895357</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>932</v>
+        <v>71</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>58.87</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,82 +5288,82 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-11-06 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>21.65</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>19.95</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,67 +5374,67 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.09</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.02</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>15.96</t>
+          <t>11.73</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-66.93</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2223.565997130559</t>
+          <t>2237.112464183381</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1281.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>773.0</t>
+          <t>897.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>485.5</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>627.28</t>
+          <t>643.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>332</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-9.664682822420978</t>
+          <t>8.064144510457766</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>94.27537838601245</t>
+          <t>105.5726948412909</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1281</v>
+        <v>932</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>16.58</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>342.05</t>
+          <t>346.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>522.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-2.39</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>75.49</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>21.65</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>82.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.86</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>20.97</t>
+          <t>21.08</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-73.03</t>
+          <t>-68.01</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,50 +1104,50 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2237.112464183381</t>
+          <t>2261.047210300429</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>2360.2</t>
+          <t>4866.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1344.9</t>
+          <t>2602.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>694.98</t>
+          <t>935.52</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>122.5471119602961</t>
+          <t>315.3217501129079</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>687.6020166755757</t>
+          <t>1375.582259952273</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>7786</v>
+        <v>12645</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24.40</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1429,33 +1429,33 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>20.87</t>
+          <t>20.97</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-73.03</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,50 +1540,50 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2237.112464183381</t>
+          <t>2261.047210300429</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>820.4</t>
+          <t>2360.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>1344.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>579.76</t>
+          <t>694.98</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>19.80985655751795</t>
+          <t>122.5471119602961</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>200.8230256847368</t>
+          <t>687.6020166755757</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>3707</v>
+        <v>7786</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-72.37</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>25.79</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,72 +1886,72 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>20.87</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-47.47</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2237.112464183381</t>
+          <t>2261.047210300429</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>820.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>416.9</t>
+          <t>659.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>628.1</t>
+          <t>579.76</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-301</t>
+          <t>160</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-13.10162873834002</t>
+          <t>19.80985655751795</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-64.71206950520195</t>
+          <t>200.8230256847368</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>122</v>
+        <v>3707</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12.86</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.14</t>
+          <t>-72.37</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,62 +2337,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>21.36</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>20.71</t>
+          <t>20.79</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-47.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-72.31</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2237.112464183381</t>
+          <t>2261.047210300429</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>295.4</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>441.8</t>
+          <t>416.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>627.74</t>
+          <t>628.1</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>-301</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3.717912235274216</t>
+          <t>-13.10162873834002</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-57.62963157992846</t>
+          <t>-64.71206950520195</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12.86</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-35.32</t>
+          <t>-33.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>21.34</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>20.63</t>
+          <t>20.71</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-69.81</t>
+          <t>-72.31</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2237.112464183381</t>
+          <t>2261.047210300429</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>337.8</t>
+          <t>295.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>522.3</t>
+          <t>441.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>629.48</t>
+          <t>627.74</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-184</t>
+          <t>-146</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>6.084218554662919</t>
+          <t>-3.717912235274216</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-40.31080484454031</t>
+          <t>-57.62963157992846</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>14.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-69.81</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2237.112464183381</t>
+          <t>2261.047210300429</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>329.6</t>
+          <t>337.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>613.6</t>
+          <t>522.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>638.44</t>
+          <t>629.48</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-284</t>
+          <t>-184</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>14.51967735451805</t>
+          <t>6.084218554662919</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-18.20138076382364</t>
+          <t>-40.31080484454031</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,79 +3630,79 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-67.00</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2237.112464183381</t>
+          <t>2261.047210300429</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>498.6</t>
+          <t>329.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>613.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>637.64</t>
+          <t>638.44</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>-284</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>20.468960648762</t>
+          <t>14.51967735451805</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>16.7121315216225</t>
+          <t>-18.20138076382364</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,17 +4066,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4086,247 +4086,247 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>21.24</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>20.46</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>2261.047210300429</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>498.6</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>637.64</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>16.7121315216225</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>181</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>5.14</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>348.66</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>2237.112464183381</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>718.6</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>644.72</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>55.92028723220176</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>1023</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>5.03</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>346.59</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
           <t>21.9</t>
@@ -4334,12 +4334,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,87 +4386,87 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10.98</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>11.41</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-2.39</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,47 +4502,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4552,27 +4552,27 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>20.37</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-66.53</t>
+          <t>-66.69</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,50 +4592,50 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2237.112464183381</t>
+          <t>2261.047210300429</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>588.2</t>
+          <t>718.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>529.4</t>
+          <t>619.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>630.6</t>
+          <t>644.72</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>14.83051744603433</t>
+          <t>21.15202049006009</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>19.7204994175936</t>
+          <t>55.92028723220176</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>286</v>
+        <v>1023</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,17 +4695,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>13.21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,72 +4938,72 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>64.95</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>21.17</t>
+          <t>21.22</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>20.19</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-66.28</t>
+          <t>-66.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2237.112464183381</t>
+          <t>2261.047210300429</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>706.8</t>
+          <t>588.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>568.7</t>
+          <t>529.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>632.6</t>
+          <t>630.6</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>13.94142981484174</t>
+          <t>14.83051744603433</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>46.26649898895357</t>
+          <t>19.7204994175936</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>71</v>
+        <v>286</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>58.87</t>
+          <t>24.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>522</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>64.95</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>21.17</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.19</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.02</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-66.93</t>
+          <t>-66.28</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2237.112464183381</t>
+          <t>2261.047210300429</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>897.6</t>
+          <t>706.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>565.0</t>
+          <t>568.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>643.38</t>
+          <t>632.6</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>138</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>8.064144510457766</t>
+          <t>13.94142981484174</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>105.5726948412909</t>
+          <t>46.26649898895357</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>932</v>
+        <v>71</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>346.59</t>
+          <t>348.66</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>22.71</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>21.08</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>21.08</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>12645.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4866.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4866.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>2602.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>935.52</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>935.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>1375.582259952273</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>12645</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>12645.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>21.99</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>20.97</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>20.97</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>7786.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>2360.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>2360.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1344.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>694.98</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>694.98</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>687.6020166755757</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>7786</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>7786.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>21.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>21.48</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>20.87</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>20.87</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>3707.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>820.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>820.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>659.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>579.76</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>579.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>200.8230256847368</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>3707</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>3707.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>21.23</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>21.36</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>20.79</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>20.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>122.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>115.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>115.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>416.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>628.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>628.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-64.71206950520195</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>122</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>21.43</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>21.34</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>20.71</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>20.71</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>74.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>295.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>295.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>441.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>627.74</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>627.74</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-57.62963157992846</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>74</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>21.5</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>20.63</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>20.63</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>112.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>337.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>337.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>522.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>629.48</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>629.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-40.31080484454031</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>112</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>21.66</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>21.26</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>20.55</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>20.55</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>87.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>329.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>329.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>613.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>638.44</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>638.4400000000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-18.20138076382364</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>87</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>21.73</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>21.24</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>20.46</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>20.46</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>181.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>498.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>498.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>635.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>637.64</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>637.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>16.7121315216225</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>181</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>20.37</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.37</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1023.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>718.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>718.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>619.1</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>644.72</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>644.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>55.92028723220176</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1023</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1023.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>21.81</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>21.22</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>20.27</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.27</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>286.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>588.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>588.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>529.4</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>630.6</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>630.6</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>19.7204994175936</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>286</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>286.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>21.87</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>21.17</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>20.19</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20.19</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>71.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>706.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>706.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>568.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>632.6</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>632.6</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>46.26649898895357</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>71</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>522.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>82.59</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>21.86</v>
+        <v>22.06</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.08</v>
+        <v>21.22</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>62.70</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-68.01</t>
+          <t>-60.93</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2261.047210300429</t>
+          <t>2329.262142857143</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4866.8</v>
+        <v>11520.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2602.3</t>
+          <t>5907.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>935.52</v>
+        <v>1592.7</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>315.3217501129079</t>
+          <t>786.0382306720229</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1375.582259952273</t>
+          <t>3374.978873747155</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>24.65</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>522.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,74 +1328,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>75.49</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>21.65</t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>21.66</v>
+        <v>21.86</v>
       </c>
       <c r="AN3" t="n">
-        <v>20.97</v>
+        <v>21.08</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-73.03</t>
+          <t>-68.01</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2261.047210300429</t>
+          <t>2329.262142857143</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2360.2</v>
+        <v>4866.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1344.9</t>
+          <t>2602.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>694.98</v>
+        <v>935.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>122.5471119602961</t>
+          <t>315.3217501129079</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>687.6020166755757</t>
+          <t>1375.582259952273</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24.40</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,33 +1853,33 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>21.48</v>
+        <v>21.66</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.87</v>
+        <v>20.97</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-73.03</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2261.047210300429</t>
+          <t>2329.262142857143</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>820.4</v>
+        <v>2360.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>1344.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>579.76</v>
+        <v>694.98</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>19.80985655751795</t>
+          <t>122.5471119602961</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>200.8230256847368</t>
+          <t>687.6020166755757</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15.04</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-72.37</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,68 +2304,68 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.36</v>
+        <v>21.48</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.79</v>
+        <v>20.87</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-47.47</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2261.047210300429</t>
+          <t>2329.262142857143</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>115.2</v>
+        <v>820.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>416.9</t>
+          <t>659.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>628.1</v>
+        <v>579.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-301</t>
+          <t>160</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-13.10162873834002</t>
+          <t>19.80985655751795</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-64.71206950520195</t>
+          <t>200.8230256847368</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.14</t>
+          <t>-72.37</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.34</v>
+        <v>21.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.71</v>
+        <v>20.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-47.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-72.31</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2261.047210300429</t>
+          <t>2329.262142857143</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>295.4</v>
+        <v>115.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>441.8</t>
+          <t>416.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>627.74</v>
+        <v>628.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>-301</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3.717912235274216</t>
+          <t>-13.10162873834002</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-57.62963157992846</t>
+          <t>-64.71206950520195</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14.63</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-35.32</t>
+          <t>-33.14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,161 +3179,161 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.3</v>
+        <v>21.34</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.63</v>
+        <v>20.71</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-72.31</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>2329.262142857143</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>441.8</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>627.74</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-146</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-3.717912235274216</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-57.62963157992846</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>12.30</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-69.81</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>2261.047210300429</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>337.8</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>522.3</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>629.48</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-184</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>6.084218554662919</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-40.31080484454031</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>12.30</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
       <c r="BN7" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.26</v>
+        <v>21.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.55</v>
+        <v>20.63</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-69.81</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2261.047210300429</t>
+          <t>2329.262142857143</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>329.6</v>
+        <v>337.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>613.6</t>
+          <t>522.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>638.4400000000001</v>
+        <v>629.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-284</t>
+          <t>-184</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>14.51967735451805</t>
+          <t>6.084218554662919</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-18.20138076382364</t>
+          <t>-40.31080484454031</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>15.22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,75 +4024,75 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.24</v>
+        <v>21.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.46</v>
+        <v>20.55</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-67.00</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2261.047210300429</t>
+          <t>2329.262142857143</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>498.6</v>
+        <v>329.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>613.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>637.64</v>
+        <v>638.4400000000001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>-284</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>20.468960648762</t>
+          <t>14.51967735451805</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>16.7121315216225</t>
+          <t>-18.20138076382364</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>13.83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,241 +4474,241 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>2329.262142857143</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>498.6</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>637.64</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>16.7121315216225</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>5.28</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>351.01</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM10" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>2261.047210300429</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>718.6</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>644.72</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>55.92028723220176</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>5.14</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>348.66</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
           <t>21.9</t>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,87 +4768,87 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>13.44</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>13.21</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AM11" t="n">
         <v>21.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.27</v>
+        <v>20.37</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-66.53</t>
+          <t>-66.69</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4970,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2261.047210300429</t>
+          <t>2329.262142857143</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>588.2</v>
+        <v>718.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>529.4</t>
+          <t>619.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>630.6</v>
+        <v>644.72</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>14.83051744603433</t>
+          <t>21.15202049006009</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>19.7204994175936</t>
+          <t>55.92028723220176</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>15.61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.28</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,68 +5314,68 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>64.95</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.17</v>
+        <v>21.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.19</v>
+        <v>20.27</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-66.28</t>
+          <t>-66.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2261.047210300429</t>
+          <t>2329.262142857143</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>706.8</v>
+        <v>588.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>568.7</t>
+          <t>529.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>632.6</v>
+        <v>630.6</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>58</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>13.94142981484174</t>
+          <t>14.83051744603433</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>46.26649898895357</t>
+          <t>19.7204994175936</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.17</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>348.66</t>
+          <t>351.01</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>98.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,94 +993,94 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.06</v>
+        <v>22.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.22</v>
+        <v>21.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-60.93</t>
+          <t>-53.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2329.262142857143</t>
+          <t>2333.68972895863</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>11520.2</v>
+        <v>12220.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5907.8</t>
+          <t>6167.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1592.7</v>
+        <v>1658.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>786.0382306720229</t>
+          <t>1043.764200039388</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>3374.978873747155</t>
+          <t>2461.257031559893</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>522.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>21.86</v>
+        <v>22.06</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.08</v>
+        <v>21.22</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>62.70</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-68.01</t>
+          <t>-60.93</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2329.262142857143</t>
+          <t>2333.68972895863</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4866.8</v>
+        <v>11520.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2602.3</t>
+          <t>5907.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>935.52</v>
+        <v>1592.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>315.3217501129079</t>
+          <t>786.0382306720229</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1375.582259952273</t>
+          <t>3374.978873747155</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>24.65</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>522.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,74 +1758,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>4.74</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>75.49</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>21.65</t>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>21.66</v>
+        <v>21.86</v>
       </c>
       <c r="AN4" t="n">
-        <v>20.97</v>
+        <v>21.08</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-73.03</t>
+          <t>-68.01</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2329.262142857143</t>
+          <t>2333.68972895863</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2360.2</v>
+        <v>4866.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1344.9</t>
+          <t>2602.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>694.98</v>
+        <v>935.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>122.5471119602961</t>
+          <t>315.3217501129079</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>687.6020166755757</t>
+          <t>1375.582259952273</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,22 +2198,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24.40</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,33 +2283,33 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.48</v>
+        <v>21.66</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.87</v>
+        <v>20.97</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-73.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2329.262142857143</t>
+          <t>2333.68972895863</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>820.4</v>
+        <v>2360.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>1344.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>579.76</v>
+        <v>694.98</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>19.80985655751795</t>
+          <t>122.5471119602961</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>200.8230256847368</t>
+          <t>687.6020166755757</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-72.37</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,68 +2734,68 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.36</v>
+        <v>21.48</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.79</v>
+        <v>20.87</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-47.47</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2329.262142857143</t>
+          <t>2333.68972895863</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>115.2</v>
+        <v>820.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>416.9</t>
+          <t>659.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>628.1</v>
+        <v>579.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-301</t>
+          <t>160</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-13.10162873834002</t>
+          <t>19.80985655751795</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-64.71206950520195</t>
+          <t>200.8230256847368</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>16.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.14</t>
+          <t>-72.37</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.34</v>
+        <v>21.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.71</v>
+        <v>20.79</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-47.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-72.31</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2329.262142857143</t>
+          <t>2333.68972895863</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>295.4</v>
+        <v>115.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>441.8</t>
+          <t>416.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>627.74</v>
+        <v>628.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>-301</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3.717912235274216</t>
+          <t>-13.10162873834002</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-57.62963157992846</t>
+          <t>-64.71206950520195</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-35.32</t>
+          <t>-33.14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,161 +3609,161 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.3</v>
+        <v>21.34</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.63</v>
+        <v>20.71</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-72.31</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>2333.68972895863</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>441.8</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>627.74</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-146</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-3.717912235274216</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-57.62963157992846</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>12.30</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
           <t>0.37</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-69.81</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>2329.262142857143</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>337.8</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>522.3</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>629.48</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-184</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>6.084218554662919</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-40.31080484454031</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>12.30</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.26</v>
+        <v>21.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.55</v>
+        <v>20.63</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-69.81</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2329.262142857143</t>
+          <t>2333.68972895863</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>329.6</v>
+        <v>337.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>613.6</t>
+          <t>522.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>638.4400000000001</v>
+        <v>629.48</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-284</t>
+          <t>-184</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>14.51967735451805</t>
+          <t>6.084218554662919</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-18.20138076382364</t>
+          <t>-40.31080484454031</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13.83</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,75 +4454,75 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.24</v>
+        <v>21.26</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.46</v>
+        <v>20.55</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-67.00</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2329.262142857143</t>
+          <t>2333.68972895863</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>498.6</v>
+        <v>329.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>613.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>637.64</v>
+        <v>638.4400000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>-284</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>20.468960648762</t>
+          <t>14.51967735451805</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>16.7121315216225</t>
+          <t>-18.20138076382364</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.44</t>
+          <t>13.15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,241 +4904,241 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>2333.68972895863</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>498.6</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>637.64</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>16.7121315216225</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>352.95</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM11" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>2329.262142857143</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>718.6</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>644.72</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>55.92028723220176</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>5.28</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>351.01</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>1114</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
           <t>21.9</t>
@@ -5146,12 +5146,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,87 +5198,87 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>12.75</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>15.61</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.46</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.85</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>21.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.27</v>
+        <v>20.37</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-66.53</t>
+          <t>-66.69</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,48 +5400,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2329.262142857143</t>
+          <t>2333.68972895863</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>588.2</v>
+        <v>718.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>529.4</t>
+          <t>619.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>630.6</v>
+        <v>644.72</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>99</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>14.83051744603433</t>
+          <t>21.15202049006009</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>19.7204994175936</t>
+          <t>55.92028723220176</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>286.0</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>351.01</t>
+          <t>352.95</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>21.45</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>21.9</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>21.4</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>95.45</t>
+          <t>80.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>92.05</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.25</v>
+        <v>22.41</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.34</v>
+        <v>21.47</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>49.89</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-53.27</t>
+          <t>-46.61</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2333.68972895863</t>
+          <t>2333.230769230769</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>12220.2</v>
+        <v>11747</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6167.7</t>
+          <t>6283.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1658.8</v>
+        <v>1683.02</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1043.764200039388</t>
+          <t>1127.65360253176</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>2461.257031559893</t>
+          <t>1589.045316239813</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>98.13</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,94 +1423,94 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.06</v>
+        <v>22.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.22</v>
+        <v>21.34</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-60.93</t>
+          <t>-53.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2333.68972895863</t>
+          <t>2333.230769230769</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>11520.2</v>
+        <v>12220.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5907.8</t>
+          <t>6167.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1592.7</v>
+        <v>1658.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>786.0382306720229</t>
+          <t>1043.764200039388</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>3374.978873747155</t>
+          <t>2461.257031559893</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>522.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>21.86</v>
+        <v>22.06</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.08</v>
+        <v>21.22</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>62.70</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-68.01</t>
+          <t>-60.93</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2333.68972895863</t>
+          <t>2333.230769230769</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4866.8</v>
+        <v>11520.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2602.3</t>
+          <t>5907.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>935.52</v>
+        <v>1592.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>315.3217501129079</t>
+          <t>786.0382306720229</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1375.582259952273</t>
+          <t>3374.978873747155</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>24.65</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>522.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,74 +2188,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>75.49</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>21.65</t>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.66</v>
+        <v>21.86</v>
       </c>
       <c r="AN5" t="n">
-        <v>20.97</v>
+        <v>21.08</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-73.03</t>
+          <t>-68.01</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2333.68972895863</t>
+          <t>2333.230769230769</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2360.2</v>
+        <v>4866.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1344.9</t>
+          <t>2602.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>694.98</v>
+        <v>935.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>122.5471119602961</t>
+          <t>315.3217501129079</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>687.6020166755757</t>
+          <t>1375.582259952273</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,22 +2628,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.40</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,33 +2713,33 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.48</v>
+        <v>21.66</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.87</v>
+        <v>20.97</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-73.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2333.68972895863</t>
+          <t>2333.230769230769</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>820.4</v>
+        <v>2360.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>1344.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>579.76</v>
+        <v>694.98</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>19.80985655751795</t>
+          <t>122.5471119602961</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>200.8230256847368</t>
+          <t>687.6020166755757</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>16.73</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-72.37</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,68 +3164,68 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.36</v>
+        <v>21.48</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.79</v>
+        <v>20.87</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-47.47</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2333.68972895863</t>
+          <t>2333.230769230769</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>115.2</v>
+        <v>820.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>416.9</t>
+          <t>659.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>628.1</v>
+        <v>579.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-301</t>
+          <t>160</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-13.10162873834002</t>
+          <t>19.80985655751795</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-64.71206950520195</t>
+          <t>200.8230256847368</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-33.14</t>
+          <t>-72.37</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.34</v>
+        <v>21.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.71</v>
+        <v>20.79</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-47.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-72.31</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2333.68972895863</t>
+          <t>2333.230769230769</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>295.4</v>
+        <v>115.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>441.8</t>
+          <t>416.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>627.74</v>
+        <v>628.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>-301</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3.717912235274216</t>
+          <t>-13.10162873834002</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-57.62963157992846</t>
+          <t>-64.71206950520195</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-35.32</t>
+          <t>-33.14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.3</v>
+        <v>21.34</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.63</v>
+        <v>20.71</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-69.81</t>
+          <t>-72.31</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2333.68972895863</t>
+          <t>2333.230769230769</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>337.8</v>
+        <v>295.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>522.3</t>
+          <t>441.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>629.48</v>
+        <v>627.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-184</t>
+          <t>-146</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>6.084218554662919</t>
+          <t>-3.717912235274216</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-40.31080484454031</t>
+          <t>-57.62963157992846</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.26</v>
+        <v>21.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.55</v>
+        <v>20.63</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-69.81</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2333.68972895863</t>
+          <t>2333.230769230769</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>329.6</v>
+        <v>337.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>613.6</t>
+          <t>522.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>638.4400000000001</v>
+        <v>629.48</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-284</t>
+          <t>-184</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>14.51967735451805</t>
+          <t>6.084218554662919</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-18.20138076382364</t>
+          <t>-40.31080484454031</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,75 +4884,75 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.24</v>
+        <v>21.26</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.46</v>
+        <v>20.55</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-67.00</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2333.68972895863</t>
+          <t>2333.230769230769</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>498.6</v>
+        <v>329.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>613.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>637.64</v>
+        <v>638.4400000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>-284</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>20.468960648762</t>
+          <t>14.51967735451805</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>16.7121315216225</t>
+          <t>-18.20138076382364</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>352.95</t>
+          <t>354.12</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>-21.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,241 +5334,241 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>21.73</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-67.00</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>2333.230769230769</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>498.6</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>635.8</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>637.64</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-137</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>20.468960648762</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>16.7121315216225</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>16.58</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>354.12</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>1077</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>21.85</t>
         </is>
       </c>
-      <c r="AM12" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>20.37</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>19.19</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-1.94</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-66.69</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>2333.68972895863</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>718.6</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>619.1</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>644.72</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>21.15202049006009</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>55.92028723220176</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>1023.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>17.11</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>5.24</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>75.70%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>-66.98%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>352.95</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>琉園-文化創意業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>文化創意業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>21.45</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
           <t>21.9</t>
@@ -5576,12 +5576,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>21.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,63 +1024,63 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>92.05</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.41</v>
+        <v>22.54</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.47</v>
+        <v>21.55</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>34.06</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-46.61</t>
+          <t>-41.64</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>11747</v>
+        <v>10460</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6283.7</t>
+          <t>6410.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1683.02</v>
+        <v>1668.72</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1127.65360253176</t>
+          <t>1098.71012254376</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1589.045316239813</t>
+          <t>939.5209826097607</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1454,63 +1454,63 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>95.45</t>
+          <t>80.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>92.05</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.25</v>
+        <v>22.41</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.34</v>
+        <v>21.47</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>49.89</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-53.27</t>
+          <t>-46.61</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>12220.2</v>
+        <v>11747</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>6167.7</t>
+          <t>6283.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1658.8</v>
+        <v>1683.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1043.764200039388</t>
+          <t>1127.65360253176</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>2461.257031559893</t>
+          <t>1589.045316239813</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>98.13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,28 +1853,28 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.06</v>
+        <v>22.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.22</v>
+        <v>21.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-60.93</t>
+          <t>-53.27</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>11520.2</v>
+        <v>12220.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5907.8</t>
+          <t>6167.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1592.7</v>
+        <v>1658.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>786.0382306720229</t>
+          <t>1043.764200039388</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>3374.978873747155</t>
+          <t>2461.257031559893</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>522.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-3.48</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>21.86</v>
+        <v>22.06</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.08</v>
+        <v>21.22</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>62.70</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-68.01</t>
+          <t>-60.93</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4866.8</v>
+        <v>11520.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2602.3</t>
+          <t>5907.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>935.52</v>
+        <v>1592.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>315.3217501129079</t>
+          <t>786.0382306720229</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1375.582259952273</t>
+          <t>3374.978873747155</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>24.65</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>522.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,74 +2618,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>75.49</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>21.65</t>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,7 +2734,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>21.66</v>
+        <v>21.86</v>
       </c>
       <c r="AN6" t="n">
-        <v>20.97</v>
+        <v>21.08</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-73.03</t>
+          <t>-68.01</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2360.2</v>
+        <v>4866.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1344.9</t>
+          <t>2602.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>694.98</v>
+        <v>935.52</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>122.5471119602961</t>
+          <t>315.3217501129079</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>687.6020166755757</t>
+          <t>1375.582259952273</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,22 +3058,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24.40</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,28 +3143,28 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>21.48</v>
+        <v>21.66</v>
       </c>
       <c r="AN7" t="n">
-        <v>20.87</v>
+        <v>20.97</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-73.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>820.4</v>
+        <v>2360.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>1344.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>579.76</v>
+        <v>694.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>19.80985655751795</t>
+          <t>122.5471119602961</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>200.8230256847368</t>
+          <t>687.6020166755757</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14.52</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-72.37</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3604,58 +3604,58 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.36</v>
+        <v>21.48</v>
       </c>
       <c r="AN8" t="n">
-        <v>20.79</v>
+        <v>20.87</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-47.47</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>115.2</v>
+        <v>820.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>416.9</t>
+          <t>659.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>628.1</v>
+        <v>579.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-301</t>
+          <t>160</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-13.10162873834002</t>
+          <t>19.80985655751795</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-64.71206950520195</t>
+          <t>200.8230256847368</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>14.52</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.14</t>
+          <t>-72.37</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,7 +4024,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.34</v>
+        <v>21.36</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.71</v>
+        <v>20.79</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-47.47</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-72.31</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>295.4</v>
+        <v>115.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>441.8</t>
+          <t>416.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>627.74</v>
+        <v>628.1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>-301</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3.717912235274216</t>
+          <t>-13.10162873834002</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-57.62963157992846</t>
+          <t>-64.71206950520195</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-35.32</t>
+          <t>-33.14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,7 +4454,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.3</v>
+        <v>21.34</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.63</v>
+        <v>20.71</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-25.27</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-69.81</t>
+          <t>-72.31</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>337.8</v>
+        <v>295.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>522.3</t>
+          <t>441.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>629.48</v>
+        <v>627.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-184</t>
+          <t>-146</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>6.084218554662919</t>
+          <t>-3.717912235274216</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-40.31080484454031</t>
+          <t>-57.62963157992846</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-46.28</t>
+          <t>-35.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4894,63 +4894,63 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.26</v>
+        <v>21.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.55</v>
+        <v>20.63</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-11.33</t>
+          <t>-25.27</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-67.90</t>
+          <t>-69.81</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>329.6</v>
+        <v>337.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>613.6</t>
+          <t>522.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>638.4400000000001</v>
+        <v>629.48</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-284</t>
+          <t>-184</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>14.51967735451805</t>
+          <t>6.084218554662919</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-18.20138076382364</t>
+          <t>-40.31080484454031</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-46.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,7 +5314,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5324,65 +5324,65 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>21.66</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.24</v>
+        <v>21.26</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.46</v>
+        <v>20.55</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-11.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>0.39</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>1.21</t>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-67.00</t>
+          <t>-67.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2333.230769230769</t>
+          <t>2332.794452347084</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>498.6</v>
+        <v>329.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>635.8</t>
+          <t>613.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>637.64</v>
+        <v>638.4400000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-137</t>
+          <t>-284</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>20.468960648762</t>
+          <t>14.51967735451805</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>16.7121315216225</t>
+          <t>-18.20138076382364</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>21.85</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>21.55</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ2"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>9949</t>
@@ -879,77 +883,77 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-06 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-13 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -959,22 +963,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.65</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -984,313 +988,4613 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12.88</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>400</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>87.23</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>76.05</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>5.06</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>24.51</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>20.24</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>21.96</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-34.53</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>9881.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>3449.2</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>7484.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1870.58</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-4035</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>957.578723642015</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>739.6857357164972</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>9881.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>33.69</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>25.17</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>70.45</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>73.86</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>-2.32</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>8.42</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>4.79</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>24.57</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>20.15</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-38.12</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>1051.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>8141.2</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>6504.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1677.1</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>997.1956305375636</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>438.8659245034805</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1051.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>28.34</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>24.05</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-1.83</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>63.18</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-2.29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>70.45</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-2.79</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>9.55</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>7.41</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>24.69</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>20.07</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>34.06</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-41.64</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>1351.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>10460</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>6410.1</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1668.72</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>4049</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>1098.71012254376</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>939.5209826097607</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1351.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>28.34</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價跌量縮</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>24.55</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>24.55</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-2.6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>24.45</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>86.94</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>80.68</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>92.05</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>10.28</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>4.36</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>7.45</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>24.71</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>19.98</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>49.89</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-46.61</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>1341.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>11747</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>6283.7</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1683.02</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>5463</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>1127.65360253176</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>1589.045316239813</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1341.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>30.75</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價跌量縮</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>24.3</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>24.45</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>98.13</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11.04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-1.39</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>95.45</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>98.48</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>9.70</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>24.41</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>65.58</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-53.27</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>3622.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>12220.2</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>6167.7</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1658.8</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>6052</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>1043.764200039388</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>2461.257031559893</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3622.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>34.22</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價跌量縮</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>25.65</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1304.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>95.00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-4.28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>7.34</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>6.82</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>7.16</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>23.57</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>72.54</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-60.93</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>33341.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>11520.2</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>5907.8</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1592.7</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>5612</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>786.0382306720229</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>3374.978873747155</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>33341.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>35.29</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>24.65</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>24.65</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>25.3</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>522.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>40.03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>4.48</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>8.32</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>22.71</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>19.7</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>62.70</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-68.01</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>12645.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>4866.8</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>2602.3</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>935.52</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>2264</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>315.3217501129079</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>1375.582259952273</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>12645.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>24.65</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>321.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>75.49</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>24.62</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>9.60</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>6.95</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>21.99</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-73.03</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>7786.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>2360.2</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>1344.9</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>694.98</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>122.5471119602961</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>687.6020166755757</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>7786.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>28.88</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>24.85</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>24.95</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>23.5</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9.81</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>24.40</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12.50</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>9.81</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>6.94</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>6.96</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>21.46</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>20.87</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>19.51</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-6.87</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-75.67</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>3707.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>820.4</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>659.5</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>579.76</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>19.80985655751795</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>200.8230256847368</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>3707.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-72.37</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>-0.59</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>2.73</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>21.23</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>19.44</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-47.47</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-75.25</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>416.9</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>628.1</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-301</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-13.10162873834002</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-64.71206950520195</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>11.76</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>75.70%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>-66.98%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>琉園-文化創意業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>13.11</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>16.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-33.14</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>-2.01</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>21.43</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>19.39</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-36.14</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-72.31</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>2349.436170212766</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>441.8</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>627.74</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-146</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-3.717912235274216</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-57.62963157992846</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>12.30</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>5.01</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>5.22</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>360.23</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>1057</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>358.35</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>文化創意業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>文化創意業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>21.0</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>935.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-24.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>76.05</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
+          <t>85.9</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>7.23</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>22.83</v>
+        <v>23.05</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.73</v>
+        <v>21.87</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>21.96</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
+          <t>27.42</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.85</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3449.2</v>
+        <v>7485.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7484.7</t>
+          <t>9852.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1870.58</v>
+        <v>2341.1</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-4035</t>
+          <t>-2367</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>957.578723642015</t>
+          <t>1114.25776003135</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>739.6857357164972</t>
+          <t>1975.992460172696</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,7 +1203,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>73.86</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-2.32</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>8.42</t>
-        </is>
+          <t>76.05</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7.36</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.66</v>
+        <v>22.83</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.63</v>
+        <v>21.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>22.73</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+          <t>21.96</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.79</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-38.12</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>8141.2</v>
+        <v>3449.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>6504.0</t>
+          <t>7484.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1677.1</v>
+        <v>1870.58</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>-4035</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>997.1956305375636</t>
+          <t>957.578723642015</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>438.8659245034805</t>
+          <t>739.6857357164972</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,59 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>82.2</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-2.79</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>9.55</t>
-        </is>
+          <t>73.86</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8.42</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.54</v>
+        <v>22.66</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.55</v>
+        <v>21.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>34.06</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
+          <t>22.73</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.75</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-41.64</t>
+          <t>-38.12</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>10460</v>
+        <v>8141.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6410.1</t>
+          <t>6504.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1668.72</v>
+        <v>1677.1</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1098.71012254376</t>
+          <t>997.1956305375636</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>939.5209826097607</t>
+          <t>438.8659245034805</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2061,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2102,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2268,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>92.05</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>10.28</t>
-        </is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>9.550000000000001</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.41</v>
+        <v>22.54</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.47</v>
+        <v>21.55</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>49.89</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+          <t>34.06</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.71</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-46.61</t>
+          <t>-41.64</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>11747</v>
+        <v>10460</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>6283.7</t>
+          <t>6410.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1683.02</v>
+        <v>1668.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1127.65360253176</t>
+          <t>1098.71012254376</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1589.045316239813</t>
+          <t>939.5209826097607</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,7 +2469,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2698,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>95.45</t>
+          <t>80.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>98.48</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>9.70</t>
-        </is>
+          <t>92.05</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10.28</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.25</v>
+        <v>22.41</v>
       </c>
       <c r="AN6" t="n">
-        <v>21.34</v>
+        <v>21.47</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>65.58</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
+          <t>49.89</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.65</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-53.27</t>
+          <t>-46.61</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>12220.2</v>
+        <v>11747</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>6167.7</t>
+          <t>6283.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1658.8</v>
+        <v>1683.02</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1043.764200039388</t>
+          <t>1127.65360253176</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>2461.257031559893</t>
+          <t>1589.045316239813</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>98.13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3088,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,95 +3103,87 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>7.34</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>6.82</t>
-        </is>
+          <t>98.48</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.06</v>
+        <v>22.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.22</v>
+        <v>21.34</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>72.54</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
+          <t>65.58</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.57</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-60.93</t>
+          <t>-53.27</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>11520.2</v>
+        <v>12220.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5907.8</t>
+          <t>6167.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1592.7</v>
+        <v>1658.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>786.0382306720229</t>
+          <t>1043.764200039388</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>3374.978873747155</t>
+          <t>2461.257031559893</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>522.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3558,7 +3510,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3612,56 +3564,48 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>8.32</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="AH8" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>6.82</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>21.86</v>
+        <v>22.06</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.08</v>
+        <v>21.22</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>62.70</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
+          <t>72.54</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.47</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-68.01</t>
+          <t>-60.93</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,48 +3624,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4866.8</v>
+        <v>11520.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2602.3</t>
+          <t>5907.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>935.52</v>
+        <v>1592.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>315.3217501129079</t>
+          <t>786.0382306720229</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1375.582259952273</t>
+          <t>3374.978873747155</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>24.65</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>522.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,74 +3852,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5.93</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>75.49</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-12-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>21.65</t>
@@ -3988,7 +3932,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,59 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>66.67</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>9.60</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3.9</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.66</v>
+        <v>21.86</v>
       </c>
       <c r="AN9" t="n">
-        <v>20.97</v>
+        <v>21.08</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>39.15</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
+          <t>62.70</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.39</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-73.03</t>
+          <t>-68.01</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4046,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2360.2</v>
+        <v>4866.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1344.9</t>
+          <t>2602.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>694.98</v>
+        <v>935.52</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>122.5471119602961</t>
+          <t>315.3217501129079</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>687.6020166755757</t>
+          <t>1375.582259952273</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4212,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4227,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,22 +4284,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.40</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4378,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4403,7 +4339,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4418,7 +4354,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4433,33 +4369,33 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,59 +4405,51 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.33</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>6.94</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.55</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.48</v>
+        <v>21.66</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.87</v>
+        <v>20.97</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.87</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
+          <t>39.15</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.33</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-73.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,48 +4468,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>820.4</v>
+        <v>2360.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>1344.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>579.76</v>
+        <v>694.98</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>19.80985655751795</t>
+          <t>122.5471119602961</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>200.8230256847368</t>
+          <t>687.6020166755757</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>12.24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-72.37</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.55</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0.08</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.36</v>
+        <v>21.48</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.79</v>
+        <v>20.87</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-47.47</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
+          <t>-6.87</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.3</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>115.2</v>
+        <v>820.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>416.9</t>
+          <t>659.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>628.1</v>
+        <v>579.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-301</t>
+          <t>160</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-13.10162873834002</t>
+          <t>19.80985655751795</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-64.71206950520195</t>
+          <t>200.8230256847368</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-33.14</t>
+          <t>-72.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-05 00:00:00</t>
+          <t>2025-12-08 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>935</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,59 +5249,51 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-2.01</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0.59</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>21.23</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.34</v>
+        <v>21.36</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.71</v>
+        <v>20.79</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-36.14</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
+          <t>-47.47</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.3</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-72.31</t>
+          <t>-75.25</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2349.436170212766</t>
+          <t>2396.68342776204</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>295.4</v>
+        <v>115.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>441.8</t>
+          <t>416.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>627.74</v>
+        <v>628.1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-146</t>
+          <t>-301</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3.717912235274216</t>
+          <t>-13.10162873834002</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-57.62963157992846</t>
+          <t>-64.71206950520195</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>358.35</t>
+          <t>354.9</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>935.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-24.03</t>
+          <t>-16.27</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.34</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>5.78</v>
+        <v>1.81</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.05</v>
+        <v>23.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.87</v>
+        <v>21.98</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-29.71</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>7485.6</v>
+        <v>8458.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9852.9</t>
+          <t>10102.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2341.1</v>
+        <v>2463.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2367</t>
+          <t>-1644</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1114.25776003135</t>
+          <t>1169.319236301561</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1975.992460172696</t>
+          <t>1472.157355787718</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>935.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-24.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>5.78</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>22.83</v>
+        <v>23.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.73</v>
+        <v>21.87</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3449.2</v>
+        <v>7485.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7484.7</t>
+          <t>9852.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1870.58</v>
+        <v>2341.1</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-4035</t>
+          <t>-2367</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>957.578723642015</t>
+          <t>1114.25776003135</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>739.6857357164972</t>
+          <t>1975.992460172696</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-2.32</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.42</v>
+        <v>7.36</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.66</v>
+        <v>22.83</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.63</v>
+        <v>21.73</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-38.12</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>8141.2</v>
+        <v>3449.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6504.0</t>
+          <t>7484.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1677.1</v>
+        <v>1870.58</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>-4035</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>997.1956305375636</t>
+          <t>957.578723642015</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>438.8659245034805</t>
+          <t>739.6857357164972</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,51 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-2.79</v>
+        <v>-2.32</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.54</v>
+        <v>22.66</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.55</v>
+        <v>21.63</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-41.64</t>
+          <t>-38.12</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>10460</v>
+        <v>8141.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>6410.1</t>
+          <t>6504.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1668.72</v>
+        <v>1677.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1098.71012254376</t>
+          <t>997.1956305375636</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>939.5209826097607</t>
+          <t>438.8659245034805</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>92.05</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-1.05</v>
+        <v>-2.79</v>
       </c>
       <c r="AI6" t="n">
-        <v>10.28</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.41</v>
+        <v>22.54</v>
       </c>
       <c r="AN6" t="n">
-        <v>21.47</v>
+        <v>21.55</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>34.06</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-46.61</t>
+          <t>-41.64</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>11747</v>
+        <v>10460</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>6283.7</t>
+          <t>6410.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1683.02</v>
+        <v>1668.72</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1127.65360253176</t>
+          <t>1098.71012254376</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1589.045316239813</t>
+          <t>939.5209826097607</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>95.45</t>
+          <t>80.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>92.05</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>2.83</v>
+        <v>-1.05</v>
       </c>
       <c r="AI7" t="n">
-        <v>9.699999999999999</v>
+        <v>10.28</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.25</v>
+        <v>22.41</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.34</v>
+        <v>21.47</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>49.89</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-53.27</t>
+          <t>-46.61</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>12220.2</v>
+        <v>11747</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6167.7</t>
+          <t>6283.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1658.8</v>
+        <v>1683.02</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1043.764200039388</t>
+          <t>1127.65360253176</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>2461.257031559893</t>
+          <t>1589.045316239813</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>98.13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3525,87 +3525,87 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>7.34</v>
+        <v>2.83</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.06</v>
+        <v>22.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.22</v>
+        <v>21.34</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-60.93</t>
+          <t>-53.27</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,48 +3624,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>11520.2</v>
+        <v>12220.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5907.8</t>
+          <t>6167.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1592.7</v>
+        <v>1658.8</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>786.0382306720229</t>
+          <t>1043.764200039388</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>3374.978873747155</t>
+          <t>2461.257031559893</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>522.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3987,47 +3987,47 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>8.32</v>
+        <v>7.34</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.9</v>
+        <v>6.82</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>21.86</v>
+        <v>22.06</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.08</v>
+        <v>21.22</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>62.70</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-68.01</t>
+          <t>-60.93</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,48 +4046,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4866.8</v>
+        <v>11520.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2602.3</t>
+          <t>5907.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>935.52</v>
+        <v>1592.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>315.3217501129079</t>
+          <t>786.0382306720229</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1375.582259952273</t>
+          <t>3374.978873747155</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>24.65</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>522.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,74 +4274,74 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>7.84</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>75.49</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-12-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>21.65</t>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,51 +4405,51 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>9.6</v>
+        <v>8.32</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.66</v>
+        <v>21.86</v>
       </c>
       <c r="AN10" t="n">
-        <v>20.97</v>
+        <v>21.08</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-73.03</t>
+          <t>-68.01</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,48 +4468,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2360.2</v>
+        <v>4866.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1344.9</t>
+          <t>2602.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>694.98</v>
+        <v>935.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>122.5471119602961</t>
+          <t>315.3217501129079</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>687.6020166755757</t>
+          <t>1375.582259952273</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12.24</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.40</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4791,33 +4791,33 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4827,51 +4827,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>6.94</v>
+        <v>9.6</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.08</v>
+        <v>1.55</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.48</v>
+        <v>21.66</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.87</v>
+        <v>20.97</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-73.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,48 +4890,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>820.4</v>
+        <v>2360.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>1344.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>579.76</v>
+        <v>694.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>19.80985655751795</t>
+          <t>122.5471119602961</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>200.8230256847368</t>
+          <t>687.6020166755757</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>163.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-72.37</t>
+          <t>24.40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-08 00:00:00</t>
+          <t>2025-12-09 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>12.50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,63 +5234,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>242</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.55</v>
+        <v>6.94</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.59</v>
+        <v>-0.08</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>21.46</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.36</v>
+        <v>21.48</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.79</v>
+        <v>20.87</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-47.47</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="AR12" t="n">
         <v>0.3</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-75.25</t>
+          <t>-75.67</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2396.68342776204</t>
+          <t>2406.460396039604</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>115.2</v>
+        <v>820.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>416.9</t>
+          <t>659.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>628.1</v>
+        <v>579.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-301</t>
+          <t>160</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-13.10162873834002</t>
+          <t>19.80985655751795</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-64.71206950520195</t>
+          <t>200.8230256847368</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>3707.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>354.9</t>
+          <t>359.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>22.95</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>20.8</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-16.27</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,56 +1024,56 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.81</v>
+        <v>-1.04</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.2</v>
+        <v>23.35</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.98</v>
+        <v>22.08</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-23.01</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>8458.6</v>
+        <v>8742</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>10102.8</t>
+          <t>9601.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2463.48</v>
+        <v>2515.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1644</t>
+          <t>-859</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1169.319236301561</t>
+          <t>1116.319176689558</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1472.157355787718</t>
+          <t>824.818848823541</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>935.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-24.03</t>
+          <t>-16.27</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,7 +1436,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1446,56 +1446,56 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.34</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>5.78</v>
+        <v>1.81</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.05</v>
+        <v>23.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.87</v>
+        <v>21.98</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-29.71</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>7485.6</v>
+        <v>8458.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>9852.9</t>
+          <t>10102.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2341.1</v>
+        <v>2463.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2367</t>
+          <t>-1644</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1114.25776003135</t>
+          <t>1169.319236301561</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1975.992460172696</t>
+          <t>1472.157355787718</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>935.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-24.03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,7 +1858,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1868,56 +1868,56 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>5.78</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>22.83</v>
+        <v>23.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.73</v>
+        <v>21.87</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3449.2</v>
+        <v>7485.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7484.7</t>
+          <t>9852.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1870.58</v>
+        <v>2341.1</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-4035</t>
+          <t>-2367</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>957.578723642015</t>
+          <t>1114.25776003135</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>739.6857357164972</t>
+          <t>1975.992460172696</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,7 +2280,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2290,56 +2290,56 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-2.32</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.42</v>
+        <v>7.36</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.66</v>
+        <v>22.83</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.63</v>
+        <v>21.73</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-38.12</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>8141.2</v>
+        <v>3449.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>6504.0</t>
+          <t>7484.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1677.1</v>
+        <v>1870.58</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>-4035</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>997.1956305375636</t>
+          <t>957.578723642015</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>438.8659245034805</t>
+          <t>739.6857357164972</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2717,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-2.79</v>
+        <v>-2.32</v>
       </c>
       <c r="AI6" t="n">
-        <v>9.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.54</v>
+        <v>22.66</v>
       </c>
       <c r="AN6" t="n">
-        <v>21.55</v>
+        <v>21.63</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-41.64</t>
+          <t>-38.12</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>10460</v>
+        <v>8141.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>6410.1</t>
+          <t>6504.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1668.72</v>
+        <v>1677.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1098.71012254376</t>
+          <t>997.1956305375636</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>939.5209826097607</t>
+          <t>438.8659245034805</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,7 +3124,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3134,56 +3134,56 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>92.05</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-1.05</v>
+        <v>-2.79</v>
       </c>
       <c r="AI7" t="n">
-        <v>10.28</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.41</v>
+        <v>22.54</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.47</v>
+        <v>21.55</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>34.06</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-46.61</t>
+          <t>-41.64</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>11747</v>
+        <v>10460</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6283.7</t>
+          <t>6410.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1683.02</v>
+        <v>1668.72</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1127.65360253176</t>
+          <t>1098.71012254376</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1589.045316239813</t>
+          <t>939.5209826097607</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,7 +3546,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3556,56 +3556,56 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>95.45</t>
+          <t>80.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>92.05</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.83</v>
+        <v>-1.05</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.699999999999999</v>
+        <v>10.28</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.25</v>
+        <v>22.41</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.34</v>
+        <v>21.47</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>49.89</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-53.27</t>
+          <t>-46.61</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,48 +3624,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>12220.2</v>
+        <v>11747</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6167.7</t>
+          <t>6283.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1658.8</v>
+        <v>1683.02</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1043.764200039388</t>
+          <t>1127.65360253176</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2461.257031559893</t>
+          <t>1589.045316239813</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>98.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -3947,28 +3947,28 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -3978,56 +3978,56 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>7.34</v>
+        <v>2.83</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.06</v>
+        <v>22.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.22</v>
+        <v>21.34</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-60.93</t>
+          <t>-53.27</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,48 +4046,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>11520.2</v>
+        <v>12220.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5907.8</t>
+          <t>6167.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1592.7</v>
+        <v>1658.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>786.0382306720229</t>
+          <t>1043.764200039388</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>3374.978873747155</t>
+          <t>2461.257031559893</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>522.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,7 +4390,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4409,47 +4409,47 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>8.32</v>
+        <v>7.34</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.9</v>
+        <v>6.82</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>21.86</v>
+        <v>22.06</v>
       </c>
       <c r="AN10" t="n">
-        <v>21.08</v>
+        <v>21.22</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>62.70</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-68.01</t>
+          <t>-60.93</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,48 +4468,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4866.8</v>
+        <v>11520.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2602.3</t>
+          <t>5907.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>935.52</v>
+        <v>1592.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>315.3217501129079</t>
+          <t>786.0382306720229</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1375.582259952273</t>
+          <t>3374.978873747155</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>24.65</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>522.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,94 +4696,94 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>75.49</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>12.88</t>
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4827,51 +4827,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>9.6</v>
+        <v>8.32</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.66</v>
+        <v>21.86</v>
       </c>
       <c r="AN11" t="n">
-        <v>20.97</v>
+        <v>21.08</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-73.03</t>
+          <t>-68.01</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,48 +4890,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2360.2</v>
+        <v>4866.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1344.9</t>
+          <t>2602.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>694.98</v>
+        <v>935.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>122.5471119602961</t>
+          <t>315.3217501129079</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>687.6020166755757</t>
+          <t>1375.582259952273</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5086,14 +5086,14 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>163.0</t>
+          <t>321.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,84 +5128,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24.40</t>
+          <t>75.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>12.88</t>
@@ -5213,28 +5213,28 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.50</t>
+          <t>24.62</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5249,51 +5249,51 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>6.94</v>
+        <v>9.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.08</v>
+        <v>1.55</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.48</v>
+        <v>21.66</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.87</v>
+        <v>20.97</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-73.03</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,125 +5312,125 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2406.460396039604</t>
+          <t>2408.925847457627</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>820.4</v>
+        <v>2360.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>659.5</t>
+          <t>1344.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>579.76</v>
+        <v>694.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>19.80985655751795</t>
+          <t>122.5471119602961</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>200.8230256847368</t>
+          <t>687.6020166755757</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3707.0</t>
+          <t>7786.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/09/11</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>28.88</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>琉園</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>文化創意業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>24.76679104477612</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-40.08623103197267</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-21.81323434808007</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>22.73</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>琉園</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>文化創意業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>24.76679104477612</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-40.08623103197267</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-21.81323434808007</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BU12" t="inlineStr">
         <is>
           <t>0.68</t>
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>65.89</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.04</v>
+        <v>2.43</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.32</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.35</v>
+        <v>23.56</v>
       </c>
       <c r="AN2" t="n">
-        <v>22.08</v>
+        <v>22.21</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-23.01</t>
+          <t>-20.01</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>2729.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>8742</v>
+        <v>9077.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9601.0</t>
+          <t>8609.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2515.54</v>
+        <v>2566.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-859</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1116.319176689558</t>
+          <t>998.1372145416301</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>824.818848823541</t>
+          <t>348.1364227280283</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>2729.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-16.27</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.81</v>
+        <v>-1.04</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.2</v>
+        <v>23.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>21.98</v>
+        <v>22.08</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-23.01</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>8458.6</v>
+        <v>8742</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>10102.8</t>
+          <t>9601.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2463.48</v>
+        <v>2515.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1644</t>
+          <t>-859</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1169.319236301561</t>
+          <t>1116.319176689558</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1472.157355787718</t>
+          <t>824.818848823541</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>935.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-24.03</t>
+          <t>-16.27</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.34</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>5.78</v>
+        <v>1.81</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>23.05</v>
+        <v>23.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.87</v>
+        <v>21.98</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-29.71</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>7485.6</v>
+        <v>8458.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>9852.9</t>
+          <t>10102.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2341.1</v>
+        <v>2463.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2367</t>
+          <t>-1644</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1114.25776003135</t>
+          <t>1169.319236301561</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1975.992460172696</t>
+          <t>1472.157355787718</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>935.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-24.03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>5.78</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>22.83</v>
+        <v>23.05</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.73</v>
+        <v>21.87</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3449.2</v>
+        <v>7485.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7484.7</t>
+          <t>9852.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1870.58</v>
+        <v>2341.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-4035</t>
+          <t>-2367</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>957.578723642015</t>
+          <t>1114.25776003135</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>739.6857357164972</t>
+          <t>1975.992460172696</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-2.32</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.42</v>
+        <v>7.36</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.66</v>
+        <v>22.83</v>
       </c>
       <c r="AN6" t="n">
-        <v>21.63</v>
+        <v>21.73</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-38.12</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>8141.2</v>
+        <v>3449.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>6504.0</t>
+          <t>7484.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1677.1</v>
+        <v>1870.58</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>-4035</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>997.1956305375636</t>
+          <t>957.578723642015</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>438.8659245034805</t>
+          <t>739.6857357164972</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-2.79</v>
+        <v>-2.32</v>
       </c>
       <c r="AI7" t="n">
-        <v>9.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.54</v>
+        <v>22.66</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.55</v>
+        <v>21.63</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-41.64</t>
+          <t>-38.12</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>10460</v>
+        <v>8141.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6410.1</t>
+          <t>6504.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1668.72</v>
+        <v>1677.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1098.71012254376</t>
+          <t>997.1956305375636</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>939.5209826097607</t>
+          <t>438.8659245034805</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>92.05</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-1.05</v>
+        <v>-2.79</v>
       </c>
       <c r="AI8" t="n">
-        <v>10.28</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.41</v>
+        <v>22.54</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.47</v>
+        <v>21.55</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>34.06</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-46.61</t>
+          <t>-41.64</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,48 +3624,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>11747</v>
+        <v>10460</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6283.7</t>
+          <t>6410.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1683.02</v>
+        <v>1668.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1127.65360253176</t>
+          <t>1098.71012254376</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1589.045316239813</t>
+          <t>939.5209826097607</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>6.32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>95.45</t>
+          <t>80.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>92.05</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2.83</v>
+        <v>-1.05</v>
       </c>
       <c r="AI9" t="n">
-        <v>9.699999999999999</v>
+        <v>10.28</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.25</v>
+        <v>22.41</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.34</v>
+        <v>21.47</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>49.89</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-53.27</t>
+          <t>-46.61</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,48 +4046,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>12220.2</v>
+        <v>11747</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6167.7</t>
+          <t>6283.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1658.8</v>
+        <v>1683.02</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1043.764200039388</t>
+          <t>1127.65360253176</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2461.257031559893</t>
+          <t>1589.045316239813</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>98.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4369,87 +4369,87 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>7.34</v>
+        <v>2.83</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.06</v>
+        <v>22.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>21.22</v>
+        <v>21.34</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-60.93</t>
+          <t>-53.27</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,48 +4468,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>11520.2</v>
+        <v>12220.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5907.8</t>
+          <t>6167.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1592.7</v>
+        <v>1658.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>786.0382306720229</t>
+          <t>1043.764200039388</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>3374.978873747155</t>
+          <t>2461.257031559893</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>522.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,12 +4812,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4831,47 +4831,47 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>8.32</v>
+        <v>7.34</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.9</v>
+        <v>6.82</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>21.86</v>
+        <v>22.06</v>
       </c>
       <c r="AN11" t="n">
-        <v>21.08</v>
+        <v>21.22</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>62.70</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-68.01</t>
+          <t>-60.93</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,48 +4890,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>4866.8</v>
+        <v>11520.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2602.3</t>
+          <t>5907.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>935.52</v>
+        <v>1592.7</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>315.3217501129079</t>
+          <t>786.0382306720229</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1375.582259952273</t>
+          <t>3374.978873747155</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>24.65</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>321.0</t>
+          <t>522.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,94 +5118,94 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>24.6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>75.49</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-12-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>24.1</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>12.88</t>
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,51 +5249,51 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>9.6</v>
+        <v>8.32</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.66</v>
+        <v>21.86</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.97</v>
+        <v>21.08</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>62.70</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-73.03</t>
+          <t>-68.01</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,48 +5312,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2408.925847457627</t>
+          <t>2411.301833568406</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2360.2</v>
+        <v>4866.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1344.9</t>
+          <t>2602.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>694.98</v>
+        <v>935.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>122.5471119602961</t>
+          <t>315.3217501129079</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>687.6020166755757</t>
+          <t>1375.582259952273</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>7786.0</t>
+          <t>12645.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>359.08</t>
+          <t>362.87</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>65.89</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>23.56</v>
+        <v>23.82</v>
       </c>
       <c r="AN2" t="n">
-        <v>22.21</v>
+        <v>22.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-20.01</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,48 +1092,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2729.0</t>
+          <t>4591.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9077.6</v>
+        <v>8019.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8609.4</t>
+          <t>5734.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>2566.92</v>
+        <v>2601.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>998.1372145416301</t>
+          <t>866.9476913649129</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>348.1364227280283</t>
+          <t>145.4053138929685</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2729.0</t>
+          <t>4591.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>41.44</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>65.89</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.04</v>
+        <v>2.43</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.32</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>23.35</v>
+        <v>23.56</v>
       </c>
       <c r="AN3" t="n">
-        <v>22.08</v>
+        <v>22.21</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-23.01</t>
+          <t>-20.01</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>2729.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>8742</v>
+        <v>9077.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>9601.0</t>
+          <t>8609.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>2515.54</v>
+        <v>2566.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-859</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1116.319176689558</t>
+          <t>998.1372145416301</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>824.818848823541</t>
+          <t>348.1364227280283</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>2729.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,17 +1615,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-16.27</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.81</v>
+        <v>-1.04</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>23.2</v>
+        <v>23.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.98</v>
+        <v>22.08</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-23.01</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,48 +1936,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>8458.6</v>
+        <v>8742</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>10102.8</t>
+          <t>9601.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2463.48</v>
+        <v>2515.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1644</t>
+          <t>-859</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1169.319236301561</t>
+          <t>1116.319176689558</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1472.157355787718</t>
+          <t>824.818848823541</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>935.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-24.03</t>
+          <t>-16.27</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.34</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>5.78</v>
+        <v>1.81</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>23.05</v>
+        <v>23.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>21.87</v>
+        <v>21.98</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-29.71</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,48 +2358,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>7485.6</v>
+        <v>8458.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>9852.9</t>
+          <t>10102.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>2341.1</v>
+        <v>2463.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2367</t>
+          <t>-1644</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1114.25776003135</t>
+          <t>1169.319236301561</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1975.992460172696</t>
+          <t>1472.157355787718</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>935.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-24.03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>5.78</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>22.83</v>
+        <v>23.05</v>
       </c>
       <c r="AN6" t="n">
-        <v>21.73</v>
+        <v>21.87</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3449.2</v>
+        <v>7485.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7484.7</t>
+          <t>9852.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1870.58</v>
+        <v>2341.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-4035</t>
+          <t>-2367</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>957.578723642015</t>
+          <t>1114.25776003135</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>739.6857357164972</t>
+          <t>1975.992460172696</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25.17</t>
+          <t>-53.92</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-2.32</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>8.42</v>
+        <v>7.36</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>22.66</v>
+        <v>22.83</v>
       </c>
       <c r="AN7" t="n">
-        <v>21.63</v>
+        <v>21.73</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-38.12</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>8141.2</v>
+        <v>3449.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6504.0</t>
+          <t>7484.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1677.1</v>
+        <v>1870.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>-4035</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>997.1956305375636</t>
+          <t>957.578723642015</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>438.8659245034805</t>
+          <t>739.6857357164972</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,12 +3546,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,51 +3561,51 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-2.79</v>
+        <v>-2.32</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>22.54</v>
+        <v>22.66</v>
       </c>
       <c r="AN8" t="n">
-        <v>21.55</v>
+        <v>21.63</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-41.64</t>
+          <t>-38.12</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,48 +3624,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>10460</v>
+        <v>8141.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6410.1</t>
+          <t>6504.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1668.72</v>
+        <v>1677.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1098.71012254376</t>
+          <t>997.1956305375636</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>939.5209826097607</t>
+          <t>438.8659245034805</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>92.05</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-1.05</v>
+        <v>-2.79</v>
       </c>
       <c r="AI9" t="n">
-        <v>10.28</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>22.41</v>
+        <v>22.54</v>
       </c>
       <c r="AN9" t="n">
-        <v>21.47</v>
+        <v>21.55</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>34.06</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-46.61</t>
+          <t>-41.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,48 +4046,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>11747</v>
+        <v>10460</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6283.7</t>
+          <t>6410.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1683.02</v>
+        <v>1668.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1127.65360253176</t>
+          <t>1098.71012254376</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1589.045316239813</t>
+          <t>939.5209826097607</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>95.45</t>
+          <t>80.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>92.05</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>2.83</v>
+        <v>-1.05</v>
       </c>
       <c r="AI10" t="n">
-        <v>9.699999999999999</v>
+        <v>10.28</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>22.25</v>
+        <v>22.41</v>
       </c>
       <c r="AN10" t="n">
-        <v>21.34</v>
+        <v>21.47</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>49.89</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-53.27</t>
+          <t>-46.61</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,48 +4468,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>12220.2</v>
+        <v>11747</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6167.7</t>
+          <t>6283.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1658.8</v>
+        <v>1683.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1043.764200039388</t>
+          <t>1127.65360253176</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2461.257031559893</t>
+          <t>1589.045316239813</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1304.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>95.00</t>
+          <t>98.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4791,87 +4791,87 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.45</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.48</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>7.34</v>
+        <v>2.83</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>22.06</v>
+        <v>22.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>21.22</v>
+        <v>21.34</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>72.54</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-60.93</t>
+          <t>-53.27</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,48 +4890,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>11520.2</v>
+        <v>12220.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5907.8</t>
+          <t>6167.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1592.7</v>
+        <v>1658.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>786.0382306720229</t>
+          <t>1043.764200039388</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3374.978873747155</t>
+          <t>2461.257031559893</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>33341.0</t>
+          <t>3622.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>522.0</t>
+          <t>1304.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>95.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-11 00:00:00</t>
+          <t>2025-12-12 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>173</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5253,47 +5253,47 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>8.32</v>
+        <v>7.34</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.9</v>
+        <v>6.82</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>21.86</v>
+        <v>22.06</v>
       </c>
       <c r="AN12" t="n">
-        <v>21.08</v>
+        <v>21.22</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>62.70</t>
+          <t>72.54</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-68.01</t>
+          <t>-60.93</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,48 +5312,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2411.301833568406</t>
+          <t>2417.604929577465</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>4866.8</v>
+        <v>11520.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2602.3</t>
+          <t>5907.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>935.52</v>
+        <v>1592.7</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>315.3217501129079</t>
+          <t>786.0382306720229</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1375.582259952273</t>
+          <t>3374.978873747155</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>12645.0</t>
+          <t>33341.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>362.87</t>
+          <t>358.57</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>24.1</t>
+          <t>24.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>27.05</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>24.65</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
-      </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>-43.16</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,66 +1094,66 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.92</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>99.22</t>
+          <t>98.31</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>3.93</v>
+        <v>2.21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.72</v>
+        <v>7.8</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>24.07</v>
+        <v>24.32</v>
       </c>
       <c r="AV2" t="n">
-        <v>22.39</v>
+        <v>22.48</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,48 +1172,48 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>4005.0</t>
+          <t>2699.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>4059.8</v>
+        <v>3358.4</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>5772.7</t>
+          <t>5908.5</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>2653.92</v>
+        <v>2678.76</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-1712</t>
+          <t>-2550</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>726.7878011335574</t>
+          <t>572.88396379259</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-44.0915951388979</t>
+          <t>-273.5871415827314</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>4005.0</t>
+          <t>2699.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>26.1</t>
-        </is>
-      </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,12 +1556,12 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1571,51 +1571,51 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>99.22</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>2.64</v>
+        <v>3.93</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.19</v>
+        <v>7.72</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>23.82</v>
+        <v>24.07</v>
       </c>
       <c r="AV3" t="n">
-        <v>22.31</v>
+        <v>22.39</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,48 +1634,48 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>4591.0</t>
+          <t>4005.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>8019.6</v>
+        <v>4059.8</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>5734.4</t>
+          <t>5772.7</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>2601.16</v>
+        <v>2653.92</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>-1712</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>866.9476913649129</t>
+          <t>726.7878011335574</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>145.4053138929685</t>
+          <t>-44.0915951388979</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>4591.0</t>
+          <t>4005.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>41.44</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,17 +1735,17 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1997,17 +1997,17 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,66 +2018,66 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>65.89</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.130000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>23.56</v>
+        <v>23.82</v>
       </c>
       <c r="AV4" t="n">
-        <v>22.21</v>
+        <v>22.31</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-20.01</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,48 +2096,48 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2729.0</t>
+          <t>4591.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>9077.6</v>
+        <v>8019.6</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>8609.4</t>
+          <t>5734.4</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>2566.92</v>
+        <v>2601.16</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>998.1372145416301</t>
+          <t>866.9476913649129</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>348.1364227280283</t>
+          <t>145.4053138929685</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>2729.0</t>
+          <t>4591.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>41.44</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,17 +2197,17 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,66 +2480,66 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>65.89</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-1.04</v>
+        <v>2.43</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.32</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>23.35</v>
+        <v>23.56</v>
       </c>
       <c r="AV5" t="n">
-        <v>22.08</v>
+        <v>22.21</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-23.01</t>
+          <t>-20.01</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,48 +2558,48 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>2729.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>8742</v>
+        <v>9077.6</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>9601.0</t>
+          <t>8609.4</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>2515.54</v>
+        <v>2566.92</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-859</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>1116.319176689558</t>
+          <t>998.1372145416301</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>824.818848823541</t>
+          <t>348.1364227280283</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>2729.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,17 +2659,17 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-16.27</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,66 +2942,66 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>1.81</v>
+        <v>-1.04</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>23.2</v>
+        <v>23.35</v>
       </c>
       <c r="AV6" t="n">
-        <v>21.98</v>
+        <v>22.08</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-23.01</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,48 +3020,48 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>8458.6</v>
+        <v>8742</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>10102.8</t>
+          <t>9601.0</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>2463.48</v>
+        <v>2515.54</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-1644</t>
+          <t>-859</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>1169.319236301561</t>
+          <t>1116.319176689558</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>1472.157355787718</t>
+          <t>824.818848823541</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,17 +3121,17 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>935.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-24.03</t>
+          <t>-16.27</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,66 +3404,66 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.34</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>5.78</v>
+        <v>1.81</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>23.05</v>
+        <v>23.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>21.87</v>
+        <v>21.98</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-29.71</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,48 +3482,48 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>7485.6</v>
+        <v>8458.6</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>9852.9</t>
+          <t>10102.8</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>2341.1</v>
+        <v>2463.48</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-2367</t>
+          <t>-1644</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1114.25776003135</t>
+          <t>1169.319236301561</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>1975.992460172696</t>
+          <t>1472.157355787718</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,17 +3583,17 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>935.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-24.03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,66 +3866,66 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>5.78</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>22.83</v>
+        <v>23.05</v>
       </c>
       <c r="AV8" t="n">
-        <v>21.73</v>
+        <v>21.87</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,48 +3944,48 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>3449.2</v>
+        <v>7485.6</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>7484.7</t>
+          <t>9852.9</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>1870.58</v>
+        <v>2341.1</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-4035</t>
+          <t>-2367</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>957.578723642015</t>
+          <t>1114.25776003135</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>739.6857357164972</t>
+          <t>1975.992460172696</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CB8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,167 +4157,167 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-53.92</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/02/11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2025/02/21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2025/01/02</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>10.95</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.41</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-12-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>12.88</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/02/11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>2025/02/21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2025/01/02</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,66 +4328,66 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-2.32</v>
+        <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8.42</v>
+        <v>7.36</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>22.66</v>
+        <v>22.83</v>
       </c>
       <c r="AV9" t="n">
-        <v>21.63</v>
+        <v>21.73</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-38.12</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,48 +4406,48 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>8141.2</v>
+        <v>3449.2</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>6504.0</t>
+          <t>7484.7</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>1677.1</v>
+        <v>1870.58</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>-4035</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>997.1956305375636</t>
+          <t>957.578723642015</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>438.8659245034805</t>
+          <t>739.6857357164972</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,17 +4507,17 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,12 +4790,12 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4805,51 +4805,51 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-2.79</v>
+        <v>-2.32</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>22.54</v>
+        <v>22.66</v>
       </c>
       <c r="AV10" t="n">
-        <v>21.55</v>
+        <v>21.63</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-41.64</t>
+          <t>-38.12</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,48 +4868,48 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>10460</v>
+        <v>8141.2</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>6410.1</t>
+          <t>6504.0</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>1668.72</v>
+        <v>1677.1</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>1098.71012254376</t>
+          <t>997.1956305375636</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>939.5209826097607</t>
+          <t>438.8659245034805</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>92.05</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-1.05</v>
+        <v>-2.79</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.28</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>22.41</v>
+        <v>22.54</v>
       </c>
       <c r="AV11" t="n">
-        <v>21.47</v>
+        <v>21.55</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>34.06</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-46.61</t>
+          <t>-41.64</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,48 +5330,48 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>11747</v>
+        <v>10460</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>6283.7</t>
+          <t>6410.1</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>1683.02</v>
+        <v>1668.72</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>1127.65360253176</t>
+          <t>1098.71012254376</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>1589.045316239813</t>
+          <t>939.5209826097607</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>98.13</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-15 00:00:00</t>
+          <t>2025-12-16 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,66 +5714,66 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>95.45</t>
+          <t>80.68</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>98.48</t>
+          <t>92.05</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>2.83</v>
+        <v>-1.05</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.699999999999999</v>
+        <v>10.28</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>22.25</v>
+        <v>22.41</v>
       </c>
       <c r="AV12" t="n">
-        <v>21.34</v>
+        <v>21.47</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.98</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>49.89</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-53.27</t>
+          <t>-46.61</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,48 +5792,48 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2422.654008438819</t>
+          <t>2424.9375</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>12220.2</v>
+        <v>11747</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>6167.7</t>
+          <t>6283.7</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>1658.8</v>
+        <v>1683.02</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>1043.764200039388</t>
+          <t>1127.65360253176</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>2461.257031559893</t>
+          <t>1589.045316239813</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>3622.0</t>
+          <t>1341.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>362.39</t>
+          <t>361.21</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.45</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>7.67</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-2.24</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>94.92</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>98.31</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>2.21</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>7.02</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>26.22</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>24.32</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>22.48</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>21.01</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>16.09</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>1.28</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>1.1</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-9.03</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>2699.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>3358.4</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>5908.5</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>2678.76</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-2550</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>572.88396379259</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-273.5871415827314</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>2699.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>43.32</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價跌量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>27.4</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>11.50</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>3.07</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>99.22</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>3.93</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>7.72</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>7.20</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>25.93</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>24.07</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>22.39</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>20.89</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>17.99</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>1.25</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>1.06</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-12.69</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>4005.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>4059.8</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>5772.7</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>2653.92</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>-1712</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>726.7878011335574</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-44.0915951388979</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>4005.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>44.12</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>2.06</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>26.1</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>26.95</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>13.27</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-0.57</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>78.29</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>2.64</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>8.19</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>6.75</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>7.45</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>25.77</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>23.82</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>22.31</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>20.77</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>16.28</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>1.18</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>1.01</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-16.62</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>4591.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>8019.6</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>5734.4</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>2601.16</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>2285</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>866.9476913649129</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>145.4053138929685</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>4591.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>41.44</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>2.02</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>26.45</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>26.7</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>26.35</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>26.45</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>8.05</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>3.83</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>97.67</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>65.89</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>2.43</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>8.130000000000001</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>6.09</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>7.55</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>23.56</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>22.21</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>20.65</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>15.02</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>1.12</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.97</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-20.01</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>2729.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>9077.6</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>8609.4</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>2566.92</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>468</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>998.1372145416301</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>348.1364227280283</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>2729.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>39.57</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.99</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>26.25</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>26.1</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>8.59</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>37.21</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-1.04</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>7.32</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>5.76</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>7.48</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>25.06</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>23.35</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>22.08</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>20.54</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>13.38</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>1.06</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>0.93</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-23.01</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>2768.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>8742</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>9601.0</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>2515.54</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-859</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>1116.319176689558</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>824.818848823541</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>2768.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>32.62</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價跌量縮</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>24.95</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>24.95</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>24.3</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>18.56</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>-3.54</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>62.79</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>83.34</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>1.81</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>7.33</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>5.55</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>7.49</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>24.9</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>23.2</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>21.98</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>20.45</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>22.15</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>1.1</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>0.9</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-25.59</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>6206.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>8458.6</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>10102.8</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>2463.48</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-1644</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>1169.319236301561</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>1472.157355787718</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>6206.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>35.56</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>26.3</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>26.5</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>25.35</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>71.70</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>2.19</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>85.9</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>5.78</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>7.23</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>5.42</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>7.47</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>24.72</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>23.05</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>21.87</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>20.35</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>27.42</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>1.09</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>0.85</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-29.71</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>23804.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>7485.6</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>9852.9</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>2341.1</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-2367</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>1114.25776003135</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>1975.992460172696</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>23804.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>39.84</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.99</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>27.0</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>24.8</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>26.15</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>30.67</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>87.23</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>76.05</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>2</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>7.36</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>5.06</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>24.51</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>22.83</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>21.73</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>20.24</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>21.96</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>0.97</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>0.79</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-34.53</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>9881.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>3449.2</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>7484.7</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>1870.58</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-4035</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>957.578723642015</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>739.6857357164972</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>9881.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>33.69</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價漲量增</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.91</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>24.6</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>25.4</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>24.6</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-2.08</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>70.45</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>73.86</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-2.32</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>8.42</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>4.79</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>7.35</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>24.57</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>22.66</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>21.63</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>20.15</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>22.73</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>0.92</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>0.75</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-38.12</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>1051.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>8141.2</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>6504.0</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>1677.1</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>1637</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>997.1956305375636</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>438.8659245034805</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>1051.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>28.34</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>24.05</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>24.5</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>-0.08</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>4.29</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-2.29</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>70.45</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>82.2</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-2.79</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>9.550000000000001</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>4.57</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>7.41</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>24.69</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>22.54</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>21.55</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>20.07</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>34.06</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>0.95</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>0.71</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-41.64</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>1351.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>10460</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>6410.1</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>1668.72</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>4049</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>1098.71012254376</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>939.5209826097607</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>1351.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>28.34</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>24.55</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>24.55</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/02/21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/01/02</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>25.15</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/13</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>4.22</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-2.04</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>80.68</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>92.05</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-1.05</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>10.28</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>7.45</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>24.71</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>22.41</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>21.47</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>19.98</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>49.89</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>0.97</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>0.65</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-46.61</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/25</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>2424.9375</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>1341.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>11747</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>6283.7</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>1683.02</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>5463</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>1127.65360253176</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>1589.045316239813</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>1341.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>18.7</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/09/11</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>30.75</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>琉園</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>文化創意業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.38</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>24.76679104477612</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-40.08623103197267</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-21.81323434808007</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>5.59</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>75.70%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>-66.98%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>361.21</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>1180</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>水晶玻璃藝品93.73%、其他6.06%、配飾0.21% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>琉園-文化創意業-上櫃</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>文化創意業右上上櫃</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>25.0</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>25.1</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>24.3</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>24.45</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>13.11</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 其他 - 文化印刷業** 文化創意業 - 工藝產業</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【b1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-43.16</t>
+          <t>-44.19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>94.92</t>
+          <t>55.81</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>98.31</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>2.21</v>
+        <v>-1.74</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.8</v>
+        <v>7.78</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>24.32</v>
+        <v>24.55</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22.48</v>
+        <v>22.55</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,48 +1212,48 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>2699.0</t>
+          <t>2893.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>3358.4</v>
+        <v>3383.4</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>5908.5</t>
+          <t>6062.7</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>2678.76</v>
+        <v>2722.66</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-2550</t>
+          <t>-2679</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>572.88396379259</t>
+          <t>421.233454662369</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-273.5871415827314</t>
+          <t>-412.8443455538463</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2699.0</t>
+          <t>2893.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>39.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>-43.16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.92</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>99.22</t>
+          <t>98.31</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>3.93</v>
+        <v>2.21</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.72</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>24.07</v>
+        <v>24.32</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22.39</v>
+        <v>22.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>4005.0</t>
+          <t>2699.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>4059.8</v>
+        <v>3358.4</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>5772.7</t>
+          <t>5908.5</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>2653.92</v>
+        <v>2678.76</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-1712</t>
+          <t>-2550</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>726.7878011335574</t>
+          <t>572.88396379259</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-44.0915951388979</t>
+          <t>-273.5871415827314</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>4005.0</t>
+          <t>2699.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>26.1</t>
-        </is>
-      </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,12 +2098,12 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>99.22</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>2.64</v>
+        <v>3.93</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.19</v>
+        <v>7.72</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>23.82</v>
+        <v>24.07</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22.31</v>
+        <v>22.39</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,48 +2176,48 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4591.0</t>
+          <t>4005.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>8019.6</v>
+        <v>4059.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>5734.4</t>
+          <t>5772.7</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>2601.16</v>
+        <v>2653.92</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>-1712</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>866.9476913649129</t>
+          <t>726.7878011335574</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>145.4053138929685</t>
+          <t>-44.0915951388979</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>4591.0</t>
+          <t>4005.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>41.44</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>65.89</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.130000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>23.56</v>
+        <v>23.82</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22.21</v>
+        <v>22.31</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-20.01</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,48 +2658,48 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>2729.0</t>
+          <t>4591.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>9077.6</v>
+        <v>8019.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>8609.4</t>
+          <t>5734.4</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>2566.92</v>
+        <v>2601.16</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>998.1372145416301</t>
+          <t>866.9476913649129</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>348.1364227280283</t>
+          <t>145.4053138929685</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2729.0</t>
+          <t>4591.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>41.44</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>65.89</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-1.04</v>
+        <v>2.43</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.32</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>23.35</v>
+        <v>23.56</v>
       </c>
       <c r="AZ6" t="n">
-        <v>22.08</v>
+        <v>22.21</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-23.01</t>
+          <t>-20.01</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,48 +3140,48 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>2729.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>8742</v>
+        <v>9077.6</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>9601.0</t>
+          <t>8609.4</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>2515.54</v>
+        <v>2566.92</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-859</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>1116.319176689558</t>
+          <t>998.1372145416301</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>824.818848823541</t>
+          <t>348.1364227280283</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>2729.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-16.27</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1.81</v>
+        <v>-1.04</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>23.2</v>
+        <v>23.35</v>
       </c>
       <c r="AZ7" t="n">
-        <v>21.98</v>
+        <v>22.08</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-23.01</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,48 +3622,48 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>8458.6</v>
+        <v>8742</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>10102.8</t>
+          <t>9601.0</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>2463.48</v>
+        <v>2515.54</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-1644</t>
+          <t>-859</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>1169.319236301561</t>
+          <t>1116.319176689558</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>1472.157355787718</t>
+          <t>824.818848823541</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>935.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-24.03</t>
+          <t>-16.27</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.34</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>5.78</v>
+        <v>1.81</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>23.05</v>
+        <v>23.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21.87</v>
+        <v>21.98</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-29.71</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,48 +4104,48 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>7485.6</v>
+        <v>8458.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>9852.9</t>
+          <t>10102.8</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>2341.1</v>
+        <v>2463.48</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-2367</t>
+          <t>-1644</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>1114.25776003135</t>
+          <t>1169.319236301561</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>1975.992460172696</t>
+          <t>1472.157355787718</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>935.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-24.03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>5.78</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>22.83</v>
+        <v>23.05</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21.73</v>
+        <v>21.87</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,48 +4586,48 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>3449.2</v>
+        <v>7485.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>7484.7</t>
+          <t>9852.9</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>1870.58</v>
+        <v>2341.1</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-4035</t>
+          <t>-2367</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>957.578723642015</t>
+          <t>1114.25776003135</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>739.6857357164972</t>
+          <t>1975.992460172696</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,164 +4799,164 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-53.92</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/02/11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/02/21</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>10.45</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-12-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/01/02</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>12.88</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/02/11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/02/21</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/01/02</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="AI10" t="inlineStr">
         <is>
           <t>2025/10/13</t>
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-2.32</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.42</v>
+        <v>7.36</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>22.66</v>
+        <v>22.83</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21.63</v>
+        <v>21.73</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-38.12</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,48 +5068,48 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>8141.2</v>
+        <v>3449.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>6504.0</t>
+          <t>7484.7</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>1677.1</v>
+        <v>1870.58</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>-4035</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>997.1956305375636</t>
+          <t>957.578723642015</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>438.8659245034805</t>
+          <t>739.6857357164972</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5487,51 +5487,51 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-2.79</v>
+        <v>-2.32</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>22.54</v>
+        <v>22.66</v>
       </c>
       <c r="AZ11" t="n">
-        <v>21.55</v>
+        <v>21.63</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-41.64</t>
+          <t>-38.12</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,48 +5550,48 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>10460</v>
+        <v>8141.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>6410.1</t>
+          <t>6504.0</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>1668.72</v>
+        <v>1677.1</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>1098.71012254376</t>
+          <t>997.1956305375636</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>939.5209826097607</t>
+          <t>438.8659245034805</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>63.18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-16 00:00:00</t>
+          <t>2025-12-17 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>4.29</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>80.68</t>
+          <t>70.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>92.05</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-1.05</v>
+        <v>-2.79</v>
       </c>
       <c r="AU12" t="n">
-        <v>10.28</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>22.41</v>
+        <v>22.54</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21.47</v>
+        <v>21.55</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>34.06</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-46.61</t>
+          <t>-41.64</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,48 +6032,48 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2424.9375</t>
+          <t>2427.622720897616</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>11747</v>
+        <v>10460</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>6283.7</t>
+          <t>6410.1</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>1683.02</v>
+        <v>1668.72</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>1127.65360253176</t>
+          <t>1098.71012254376</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>1589.045316239813</t>
+          <t>939.5209826097607</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>1341.0</t>
+          <t>1351.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>361.21</t>
+          <t>363.01</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>價_量;【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-44.19</t>
+          <t>-41.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>55.81</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1153,47 +1153,47 @@
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.74</v>
+        <v>1.35</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.78</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>24.55</v>
+        <v>24.85</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22.55</v>
+        <v>22.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,24 +1212,24 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>2893.0</t>
+          <t>4406.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>3383.4</v>
+        <v>3718.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>6062.7</t>
+          <t>6398.2</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>2722.66</v>
+        <v>2793.86</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
@@ -1238,22 +1238,22 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>421.233454662369</t>
+          <t>296.9624186074229</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-412.8443455538463</t>
+          <t>-386.5282796947804</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2893.0</t>
+          <t>4406.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>44.39</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
+          <t>25.35</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
           <t>27.35</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>25.3</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-43.16</t>
+          <t>-44.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>11.20</t>
+          <t>7.88</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>94.92</t>
+          <t>55.81</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>98.31</t>
+          <t>83.58</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2.21</v>
+        <v>-1.74</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>7.78</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>24.32</v>
+        <v>24.55</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22.48</v>
+        <v>22.55</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>21.12</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-6.99</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,48 +1694,48 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>2699.0</t>
+          <t>2893.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>3358.4</v>
+        <v>3383.4</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>5908.5</t>
+          <t>6062.7</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>2678.76</v>
+        <v>2722.66</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-2550</t>
+          <t>-2679</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>572.88396379259</t>
+          <t>421.233454662369</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-273.5871415827314</t>
+          <t>-412.8443455538463</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2699.0</t>
+          <t>2893.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>39.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-29.67</t>
+          <t>-43.16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>11.20</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>11.50</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>94.92</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>99.22</t>
+          <t>98.31</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>3.93</v>
+        <v>2.21</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.72</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7.20</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>26.22</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>24.07</v>
+        <v>24.32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22.39</v>
+        <v>22.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>20.89</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-12.69</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,48 +2176,48 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>4005.0</t>
+          <t>2699.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>4059.8</v>
+        <v>3358.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>5772.7</t>
+          <t>5908.5</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>2653.92</v>
+        <v>2678.76</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-1712</t>
+          <t>-2550</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>726.7878011335574</t>
+          <t>572.88396379259</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-44.0915951388979</t>
+          <t>-273.5871415827314</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>4005.0</t>
+          <t>2699.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
+          <t>27.0</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>26.1</t>
-        </is>
-      </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>-29.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>11.50</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2595,51 +2595,51 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>78.29</t>
+          <t>99.22</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>2.64</v>
+        <v>3.93</v>
       </c>
       <c r="AU5" t="n">
-        <v>8.19</v>
+        <v>7.72</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>7.20</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>23.82</v>
+        <v>24.07</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22.31</v>
+        <v>22.39</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>20.89</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>16.28</t>
+          <t>17.99</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-12.69</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,48 +2658,48 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>4591.0</t>
+          <t>4005.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>8019.6</v>
+        <v>4059.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>5734.4</t>
+          <t>5772.7</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>2601.16</v>
+        <v>2653.92</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>-1712</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>866.9476913649129</t>
+          <t>726.7878011335574</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>145.4053138929685</t>
+          <t>-44.0915951388979</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>4591.0</t>
+          <t>4005.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>41.44</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>39.85</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>8.30</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>65.89</t>
+          <t>78.29</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.130000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>23.56</v>
+        <v>23.82</v>
       </c>
       <c r="AZ6" t="n">
-        <v>22.21</v>
+        <v>22.31</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.77</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>16.28</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-20.01</t>
+          <t>-16.62</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,48 +3140,48 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>2729.0</t>
+          <t>4591.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>9077.6</v>
+        <v>8019.6</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>8609.4</t>
+          <t>5734.4</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>2566.92</v>
+        <v>2601.16</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>998.1372145416301</t>
+          <t>866.9476913649129</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>348.1364227280283</t>
+          <t>145.4053138929685</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2729.0</t>
+          <t>4591.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>39.57</t>
+          <t>41.44</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>8.30</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>37.21</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>65.89</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.04</v>
+        <v>2.43</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.32</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>25.06</t>
+          <t>25.48</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>23.35</v>
+        <v>23.56</v>
       </c>
       <c r="AZ7" t="n">
-        <v>22.08</v>
+        <v>22.21</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.93</v>
+        <v>0.97</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-23.01</t>
+          <t>-20.01</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,48 +3622,48 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>2729.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>8742</v>
+        <v>9077.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>9601.0</t>
+          <t>8609.4</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>2515.54</v>
+        <v>2566.92</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-859</t>
+          <t>468</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>1116.319176689558</t>
+          <t>998.1372145416301</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>824.818848823541</t>
+          <t>348.1364227280283</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>2768.0</t>
+          <t>2729.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>32.62</t>
+          <t>39.57</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>24.95</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>242.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-16.27</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-3.54</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>62.79</t>
+          <t>37.21</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1.81</v>
+        <v>-1.04</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>23.2</v>
+        <v>23.35</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21.98</v>
+        <v>22.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20.45</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>22.15</t>
+          <t>13.38</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-25.59</t>
+          <t>-23.01</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,48 +4104,48 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>8458.6</v>
+        <v>8742</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>10102.8</t>
+          <t>9601.0</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>2463.48</v>
+        <v>2515.54</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-1644</t>
+          <t>-859</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>1169.319236301561</t>
+          <t>1116.319176689558</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>1472.157355787718</t>
+          <t>824.818848823541</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>6206.0</t>
+          <t>2768.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>32.62</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4205,17 +4205,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>24.95</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>935.0</t>
+          <t>242.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-24.03</t>
+          <t>-16.27</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>71.70</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-3.54</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>62.79</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.34</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>5.78</v>
+        <v>1.81</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>23.05</v>
+        <v>23.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21.87</v>
+        <v>21.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>20.45</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>22.15</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-29.71</t>
+          <t>-25.59</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,48 +4586,48 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>7485.6</v>
+        <v>8458.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>9852.9</t>
+          <t>10102.8</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>2341.1</v>
+        <v>2463.48</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-2367</t>
+          <t>-1644</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>1114.25776003135</t>
+          <t>1169.319236301561</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>1975.992460172696</t>
+          <t>1472.157355787718</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>23804.0</t>
+          <t>6206.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>24.8</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>25.35</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>935.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-53.92</t>
+          <t>-24.03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>71.70</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>76.05</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>5.78</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>24.51</t>
+          <t>24.72</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>22.83</v>
+        <v>23.05</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21.73</v>
+        <v>21.87</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20.24</t>
+          <t>20.35</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>27.42</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>0.97</v>
+        <v>1.09</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-34.53</t>
+          <t>-29.71</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,48 +5068,48 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>3449.2</v>
+        <v>7485.6</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>7484.7</t>
+          <t>9852.9</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>1870.58</v>
+        <v>2341.1</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-4035</t>
+          <t>-2367</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>957.578723642015</t>
+          <t>1114.25776003135</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>739.6857357164972</t>
+          <t>1975.992460172696</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>9881.0</t>
+          <t>23804.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>33.69</t>
+          <t>39.84</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,164 +5281,164 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>7.41</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-53.92</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-11-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>24.1</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>21.65</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>21.35</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>12.88</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/02/11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>25.45</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2025/02/21</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>24.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>7.69</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>25.17</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-12-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-11-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>24.1</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/01/02</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>25.15</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
         <is>
           <t>21.35</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>12.88</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/02/11</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>25.45</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2025/02/21</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/01/02</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>25.15</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>21.35</t>
-        </is>
-      </c>
       <c r="AI11" t="inlineStr">
         <is>
           <t>2025/10/13</t>
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>70.45</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.05</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-2.32</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.42</v>
+        <v>7.36</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>24.51</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>22.66</v>
+        <v>22.83</v>
       </c>
       <c r="AZ11" t="n">
-        <v>21.63</v>
+        <v>21.73</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>20.24</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-38.12</t>
+          <t>-34.53</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,48 +5550,48 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>8141.2</v>
+        <v>3449.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>6504.0</t>
+          <t>7484.7</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>1677.1</v>
+        <v>1870.58</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>-4035</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>997.1956305375636</t>
+          <t>957.578723642015</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>438.8659245034805</t>
+          <t>739.6857357164972</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1051.0</t>
+          <t>9881.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>33.69</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>25.17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-17 00:00:00</t>
+          <t>2025-12-18 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,12 +5954,12 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>164</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5969,51 +5969,51 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-2.79</v>
+        <v>-2.32</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>22.54</v>
+        <v>22.66</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21.55</v>
+        <v>21.63</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.15</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-41.64</t>
+          <t>-38.12</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,48 +6032,48 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2427.622720897616</t>
+          <t>2433.478991596638</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>10460</v>
+        <v>8141.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>6410.1</t>
+          <t>6504.0</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>1668.72</v>
+        <v>1677.1</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>1098.71012254376</t>
+          <t>997.1956305375636</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>939.5209826097607</t>
+          <t>438.8659245034805</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>1351.0</t>
+          <t>1051.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>363.01</t>
+          <t>368.08</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">

--- a/Result/checksun_type/工藝產業.xlsx
+++ b/Result/checksun_type/工藝產業.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>402.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-41.88</t>
+          <t>-23.18</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-18 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>13.49</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>30.83</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1149,51 +1149,51 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>83.58</t>
+          <t>85.27</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1.35</v>
+        <v>1.98</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>6.57</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>24.85</v>
+        <v>25.17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>22.66</v>
+        <v>22.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>21.37</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,48 +1212,48 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2433.478991596638</t>
+          <t>2453.160839160839</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>4406.0</t>
+          <t>11004.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>3718.8</v>
+        <v>5001.4</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>6398.2</t>
+          <t>6510.5</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>2793.86</v>
+        <v>3009.82</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-2679</t>
+          <t>-1509</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>296.9624186074229</t>
+          <t>272.2614578061171</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-386.5282796947804</t>
+          <t>136.4061733989347</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>4406.0</t>
+          <t>11004.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>44.39</t>
+          <t>46.26</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>368.08</t>
+          <t>367.0</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
           <t>27.35</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>25.35</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>27.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-44.19</t>
+          <t>-41.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-18 00:00:00</t>
+          <t>2025-12-19 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>7.88</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,12 +1621,12 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>55.81</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1635,47 +1635,47 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.74</v>
+        <v>1.35</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.78</v>
+        <v>7.2</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>24.55</v>
+        <v>24.85</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22.55</v>
+        <v>22.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>8.51</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-6.99</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,24 +1694,24 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2433.478991596638</t>
+          <t>2453.160839160839</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>2893.0</t>
+          <t>4406.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>3383.4</v>
+        <v>3718.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>6062.7</t>
+          <t>6398.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>2722.66</v>
+        <v>2793.86</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
@@ -1720,22 +1720,22 @@
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>421.233454662369</t>
+          <t>296.9624186074229</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-412.8443455538463</t>
+          <t>-386.5282796947804</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2893.0</t>
+          <t>4406.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>44.39</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t